--- a/Hoadon/HDRa/10/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDRa/10/HDDienTuMayTinhTien.xlsx
@@ -313,12 +313,12 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MHF</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>1280</t>
+          <t>761</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
@@ -328,29 +328,41 @@
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>3502348621</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẦU TƯ HAFI</t>
-        </is>
-      </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>3502543213</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>BẢO TÀNG - THƯ VIỆN TỈNH BÀ RỊA - VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>04 Phạm Văn Đồng, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K7" s="6"/>
       <c r="L7" s="13" t="n">
-        <v>3703704.0</v>
+        <v>8102487.0</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>296296.0</v>
+        <v>648199.0</v>
       </c>
       <c r="N7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>4000000.0</v>
+        <v>8750686.0</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -374,12 +386,12 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25MHF</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>762</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -389,12 +401,12 @@
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>3502348621</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẦU TƯ HAFI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="H8" s="7"/>
@@ -402,16 +414,16 @@
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
       <c r="L8" s="13" t="n">
-        <v>1185185.0</v>
+        <v>273806.0</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>94815.0</v>
+        <v>21904.0</v>
       </c>
       <c r="N8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>1280000.0</v>
+        <v>295710.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -435,12 +447,12 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25MHF</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>1282</t>
+          <t>763</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -450,41 +462,41 @@
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>3502348621</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN ĐẦU TƯ HAFI</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="H9" s="7" t="inlineStr">
         <is>
-          <t>0105965911</t>
+          <t>0100109120-008</t>
         </is>
       </c>
       <c r="I9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY TNHH SỰ KIỆN VÀ TRUYỀN THÔNG DU LỊCH VIỆT</t>
+          <t>CHI CỤC ĐĂNG KIỂM SỐ 9</t>
         </is>
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Số nhà C15, ngõ 369 đường Trường Chinh, Phường Khương Đình, Thành phố Hà Nội, Việt Nam</t>
+          <t>Số 102 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
         </is>
       </c>
       <c r="K9" s="6"/>
       <c r="L9" s="13" t="n">
-        <v>1.3037037E7</v>
+        <v>1587326.0</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>1042963.0</v>
+        <v>126986.0</v>
       </c>
       <c r="N9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>1.408E7</v>
+        <v>1714312.0</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -492,6 +504,298 @@
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>764</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>3500966118</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG ĐOÀN CƠ SỞ LIÊN DOANH VIỆT - NGA VIETSOVPETRO</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Số 105 Lê Lợi, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K10" s="6"/>
+      <c r="L10" s="13" t="n">
+        <v>4288503.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>343080.0</v>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O10" s="13" t="n">
+        <v>4631583.0</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>765</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>3500966118</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG ĐOÀN CƠ SỞ LIÊN DOANH VIỆT - NGA VIETSOVPETRO</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Số 105 Lê Lợi, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K11" s="6"/>
+      <c r="L11" s="13" t="n">
+        <v>2839048.0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>227124.0</v>
+      </c>
+      <c r="N11" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="13" t="n">
+        <v>3066172.0</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>3500966118</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG ĐOÀN CƠ SỞ LIÊN DOANH VIỆT - NGA VIETSOVPETRO</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Số 105 Lê Lợi, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K12" s="6"/>
+      <c r="L12" s="13" t="n">
+        <v>2801672.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>224134.0</v>
+      </c>
+      <c r="N12" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O12" s="13" t="n">
+        <v>3025806.0</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>767</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>01/10/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>0303587958-001</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>NHÀ KHÁCH THẮNG LỢI VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Số 149 Thùy Vân, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K13" s="6"/>
+      <c r="L13" s="13" t="n">
+        <v>4578877.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>366310.0</v>
+      </c>
+      <c r="N13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O13" s="13" t="n">
+        <v>4945187.0</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HDRa/10/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDRa/10/HDDienTuMayTinhTien.xlsx
@@ -1095,6 +1095,494 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H20" s="7"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="13" t="n">
+        <v>564815.0</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>45185.0</v>
+      </c>
+      <c r="N20" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O20" s="13" t="n">
+        <v>610000.0</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H21" s="7"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="13" t="n">
+        <v>935186.0</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>74814.0</v>
+      </c>
+      <c r="N21" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O21" s="13" t="n">
+        <v>1010000.0</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>08/10/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H22" s="7"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="13" t="n">
+        <v>814815.0</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>65185.0</v>
+      </c>
+      <c r="N22" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O22" s="13" t="n">
+        <v>880000.0</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>08/10/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H23" s="7"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="13" t="n">
+        <v>787037.0</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>62963.0</v>
+      </c>
+      <c r="N23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O23" s="13" t="n">
+        <v>850000.0</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>09/10/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H24" s="7"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="13" t="n">
+        <v>967594.0</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>77406.0</v>
+      </c>
+      <c r="N24" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O24" s="13" t="n">
+        <v>1045000.0</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>09/10/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H25" s="7"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="13" t="n">
+        <v>740740.0</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>59260.0</v>
+      </c>
+      <c r="N25" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O25" s="13" t="n">
+        <v>800000.0</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H26" s="7"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="13" t="n">
+        <v>744782.0</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>60218.0</v>
+      </c>
+      <c r="N26" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O26" s="13" t="n">
+        <v>805000.0</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H27" s="7"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="13" t="n">
+        <v>907407.0</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>72593.0</v>
+      </c>
+      <c r="N27" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O27" s="13" t="n">
+        <v>980000.0</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:Q3"/>

--- a/Hoadon/HDRa/10/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDRa/10/HDDienTuMayTinhTien.xlsx
@@ -1583,6 +1583,250 @@
         </is>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>11/10/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H28" s="7"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="13" t="n">
+        <v>1037038.0</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>82962.0</v>
+      </c>
+      <c r="N28" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O28" s="13" t="n">
+        <v>1120000.0</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>11/10/2025</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H29" s="7"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="13" t="n">
+        <v>1101851.0</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>88149.0</v>
+      </c>
+      <c r="N29" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O29" s="13" t="n">
+        <v>1190000.0</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>12/10/2025</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H30" s="7"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="13" t="n">
+        <v>879629.0</v>
+      </c>
+      <c r="M30" s="13" t="n">
+        <v>70371.0</v>
+      </c>
+      <c r="N30" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O30" s="13" t="n">
+        <v>950000.0</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>12/10/2025</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H31" s="7"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="13" t="n">
+        <v>916666.0</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <v>73334.0</v>
+      </c>
+      <c r="N31" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O31" s="13" t="n">
+        <v>990000.0</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A3:Q3"/>

--- a/Hoadon/HDRa/10/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDRa/10/HDDienTuMayTinhTien.xlsx
@@ -313,44 +313,56 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>281</t>
+          <t>761</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H7" s="7"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H7" s="7" t="inlineStr">
+        <is>
+          <t>3502543213</t>
+        </is>
+      </c>
+      <c r="I7" s="6" t="inlineStr">
+        <is>
+          <t>BẢO TÀNG - THƯ VIỆN TỈNH BÀ RỊA - VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>04 Phạm Văn Đồng, Phường Bà Rịa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K7" s="6"/>
       <c r="L7" s="13" t="n">
-        <v>787626.0</v>
+        <v>8102487.0</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>64374.0</v>
+        <v>648199.0</v>
       </c>
       <c r="N7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>852000.0</v>
+        <v>8750686.0</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -374,27 +386,27 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>762</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>02/10/2025</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="H8" s="7"/>
@@ -402,16 +414,16 @@
       <c r="J8" s="6"/>
       <c r="K8" s="6"/>
       <c r="L8" s="13" t="n">
-        <v>578519.0</v>
+        <v>273806.0</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>41481.0</v>
+        <v>21904.0</v>
       </c>
       <c r="N8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>620000.0</v>
+        <v>295710.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -435,44 +447,56 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>763</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H9" s="7"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H9" s="7" t="inlineStr">
+        <is>
+          <t>0100109120-008</t>
+        </is>
+      </c>
+      <c r="I9" s="6" t="inlineStr">
+        <is>
+          <t>CHI CỤC ĐĂNG KIỂM SỐ 9</t>
+        </is>
+      </c>
+      <c r="J9" s="6" t="inlineStr">
+        <is>
+          <t>Số 102 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K9" s="6"/>
       <c r="L9" s="13" t="n">
-        <v>793637.0</v>
+        <v>1587326.0</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>46363.0</v>
+        <v>126986.0</v>
       </c>
       <c r="N9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>840000.0</v>
+        <v>1714312.0</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -496,44 +520,56 @@
       </c>
       <c r="C10" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>284</t>
+          <t>764</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H10" s="7"/>
-      <c r="I10" s="6"/>
-      <c r="J10" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
+        <is>
+          <t>3500966118</t>
+        </is>
+      </c>
+      <c r="I10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG ĐOÀN CƠ SỞ LIÊN DOANH VIỆT - NGA VIETSOVPETRO</t>
+        </is>
+      </c>
+      <c r="J10" s="6" t="inlineStr">
+        <is>
+          <t>Số 105 Lê Lợi, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K10" s="6"/>
       <c r="L10" s="13" t="n">
-        <v>822222.0</v>
+        <v>4288503.0</v>
       </c>
       <c r="M10" s="13" t="n">
-        <v>65778.0</v>
+        <v>343080.0</v>
       </c>
       <c r="N10" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O10" s="13" t="n">
-        <v>888000.0</v>
+        <v>4631583.0</v>
       </c>
       <c r="P10" s="6" t="inlineStr">
         <is>
@@ -557,44 +593,56 @@
       </c>
       <c r="C11" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D11" s="7" t="inlineStr">
         <is>
-          <t>285</t>
+          <t>765</t>
         </is>
       </c>
       <c r="E11" s="7" t="inlineStr">
         <is>
-          <t>03/10/2025</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G11" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H11" s="7"/>
-      <c r="I11" s="6"/>
-      <c r="J11" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H11" s="7" t="inlineStr">
+        <is>
+          <t>3500966118</t>
+        </is>
+      </c>
+      <c r="I11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG ĐOÀN CƠ SỞ LIÊN DOANH VIỆT - NGA VIETSOVPETRO</t>
+        </is>
+      </c>
+      <c r="J11" s="6" t="inlineStr">
+        <is>
+          <t>Số 105 Lê Lợi, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K11" s="6"/>
       <c r="L11" s="13" t="n">
-        <v>741818.0</v>
+        <v>2839048.0</v>
       </c>
       <c r="M11" s="13" t="n">
-        <v>74182.0</v>
+        <v>227124.0</v>
       </c>
       <c r="N11" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O11" s="13" t="n">
-        <v>816000.0</v>
+        <v>3066172.0</v>
       </c>
       <c r="P11" s="6" t="inlineStr">
         <is>
@@ -618,44 +666,56 @@
       </c>
       <c r="C12" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>766</t>
         </is>
       </c>
       <c r="E12" s="7" t="inlineStr">
         <is>
-          <t>04/10/2025</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H12" s="7"/>
-      <c r="I12" s="6"/>
-      <c r="J12" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
+        <is>
+          <t>3500966118</t>
+        </is>
+      </c>
+      <c r="I12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG ĐOÀN CƠ SỞ LIÊN DOANH VIỆT - NGA VIETSOVPETRO</t>
+        </is>
+      </c>
+      <c r="J12" s="6" t="inlineStr">
+        <is>
+          <t>Số 105 Lê Lợi, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K12" s="6"/>
       <c r="L12" s="13" t="n">
-        <v>744444.0</v>
+        <v>2801672.0</v>
       </c>
       <c r="M12" s="13" t="n">
-        <v>35556.0</v>
+        <v>224134.0</v>
       </c>
       <c r="N12" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O12" s="13" t="n">
-        <v>780000.0</v>
+        <v>3025806.0</v>
       </c>
       <c r="P12" s="6" t="inlineStr">
         <is>
@@ -679,44 +739,56 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
         <is>
-          <t>287</t>
+          <t>767</t>
         </is>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>04/10/2025</t>
+          <t>01/10/2025</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G13" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H13" s="7"/>
-      <c r="I13" s="6"/>
-      <c r="J13" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H13" s="7" t="inlineStr">
+        <is>
+          <t>0303587958-001</t>
+        </is>
+      </c>
+      <c r="I13" s="6" t="inlineStr">
+        <is>
+          <t>NHÀ KHÁCH THẮNG LỢI VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J13" s="6" t="inlineStr">
+        <is>
+          <t>Số 149 Thùy Vân, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K13" s="6"/>
       <c r="L13" s="13" t="n">
-        <v>657407.0</v>
+        <v>4578877.0</v>
       </c>
       <c r="M13" s="13" t="n">
-        <v>52593.0</v>
+        <v>366310.0</v>
       </c>
       <c r="N13" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O13" s="13" t="n">
-        <v>710000.0</v>
+        <v>4945187.0</v>
       </c>
       <c r="P13" s="6" t="inlineStr">
         <is>
@@ -740,44 +812,56 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>768</t>
         </is>
       </c>
       <c r="E14" s="7" t="inlineStr">
         <is>
-          <t>05/10/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H14" s="7"/>
-      <c r="I14" s="6"/>
-      <c r="J14" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H14" s="7" t="inlineStr">
+        <is>
+          <t>3500614211</t>
+        </is>
+      </c>
+      <c r="I14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN KHOA HỌC CÔNG NGHỆ VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="J14" s="6" t="inlineStr">
+        <is>
+          <t>Số 6 đường 3 tháng 2, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K14" s="6"/>
       <c r="L14" s="13" t="n">
-        <v>942862.0</v>
+        <v>979882.0</v>
       </c>
       <c r="M14" s="13" t="n">
-        <v>91138.0</v>
+        <v>78391.0</v>
       </c>
       <c r="N14" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O14" s="13" t="n">
-        <v>1034000.0</v>
+        <v>1058273.0</v>
       </c>
       <c r="P14" s="6" t="inlineStr">
         <is>
@@ -801,44 +885,56 @@
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D15" s="7" t="inlineStr">
         <is>
-          <t>289</t>
+          <t>769</t>
         </is>
       </c>
       <c r="E15" s="7" t="inlineStr">
         <is>
-          <t>05/10/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G15" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H15" s="7"/>
-      <c r="I15" s="6"/>
-      <c r="J15" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H15" s="7" t="inlineStr">
+        <is>
+          <t>3500614211</t>
+        </is>
+      </c>
+      <c r="I15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN KHOA HỌC CÔNG NGHỆ VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="J15" s="6" t="inlineStr">
+        <is>
+          <t>Số 6 đường 3 tháng 2, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K15" s="6"/>
       <c r="L15" s="13" t="n">
-        <v>1110908.0</v>
+        <v>391500.0</v>
       </c>
       <c r="M15" s="13" t="n">
-        <v>90092.0</v>
+        <v>31320.0</v>
       </c>
       <c r="N15" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O15" s="13" t="n">
-        <v>1201000.0</v>
+        <v>422820.0</v>
       </c>
       <c r="P15" s="6" t="inlineStr">
         <is>
@@ -862,44 +958,56 @@
       </c>
       <c r="C16" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D16" s="7" t="inlineStr">
         <is>
-          <t>290</t>
+          <t>770</t>
         </is>
       </c>
       <c r="E16" s="7" t="inlineStr">
         <is>
-          <t>05/10/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H16" s="7"/>
-      <c r="I16" s="6"/>
-      <c r="J16" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H16" s="7" t="inlineStr">
+        <is>
+          <t>3500673707</t>
+        </is>
+      </c>
+      <c r="I16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DƯỢC PHẨM VÀ TRANG THIẾT BỊ Y TẾ VĨNH KHANG</t>
+        </is>
+      </c>
+      <c r="J16" s="6" t="inlineStr">
+        <is>
+          <t>Nhà số 30 Khu nhà ở Phước Sơn (Đường 11), đường 2/9, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K16" s="6"/>
       <c r="L16" s="13" t="n">
-        <v>1034005.0</v>
+        <v>1920000.0</v>
       </c>
       <c r="M16" s="13" t="n">
-        <v>82995.0</v>
+        <v>192000.0</v>
       </c>
       <c r="N16" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O16" s="13" t="n">
-        <v>1117000.0</v>
+        <v>2112000.0</v>
       </c>
       <c r="P16" s="6" t="inlineStr">
         <is>
@@ -923,44 +1031,56 @@
       </c>
       <c r="C17" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
         <is>
-          <t>291</t>
+          <t>771</t>
         </is>
       </c>
       <c r="E17" s="7" t="inlineStr">
         <is>
-          <t>05/10/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G17" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H17" s="7"/>
-      <c r="I17" s="6"/>
-      <c r="J17" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H17" s="7" t="inlineStr">
+        <is>
+          <t>3500673707</t>
+        </is>
+      </c>
+      <c r="I17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DƯỢC PHẨM VÀ TRANG THIẾT BỊ Y TẾ VĨNH KHANG</t>
+        </is>
+      </c>
+      <c r="J17" s="6" t="inlineStr">
+        <is>
+          <t>Nhà số 30 Khu nhà ở Phước Sơn (Đường 11), đường 2/9, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K17" s="6"/>
       <c r="L17" s="13" t="n">
-        <v>691482.0</v>
+        <v>1054410.0</v>
       </c>
       <c r="M17" s="13" t="n">
-        <v>38518.0</v>
+        <v>84353.0</v>
       </c>
       <c r="N17" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O17" s="13" t="n">
-        <v>730000.0</v>
+        <v>1138763.0</v>
       </c>
       <c r="P17" s="6" t="inlineStr">
         <is>
@@ -984,44 +1104,56 @@
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D18" s="7" t="inlineStr">
         <is>
-          <t>292</t>
+          <t>772</t>
         </is>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G18" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H18" s="7"/>
-      <c r="I18" s="6"/>
-      <c r="J18" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H18" s="7" t="inlineStr">
+        <is>
+          <t>0101335193-028</t>
+        </is>
+      </c>
+      <c r="I18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY BẢO HIỂM VIETINBANK VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J18" s="6" t="inlineStr">
+        <is>
+          <t>Số 19 Phạm Ngọc Thạch, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K18" s="6"/>
       <c r="L18" s="13" t="n">
-        <v>1169630.0</v>
+        <v>3232217.0</v>
       </c>
       <c r="M18" s="13" t="n">
-        <v>50370.0</v>
+        <v>258577.0</v>
       </c>
       <c r="N18" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O18" s="13" t="n">
-        <v>1220000.0</v>
+        <v>3490794.0</v>
       </c>
       <c r="P18" s="6" t="inlineStr">
         <is>
@@ -1045,44 +1177,56 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D19" s="7" t="inlineStr">
         <is>
-          <t>293</t>
+          <t>773</t>
         </is>
       </c>
       <c r="E19" s="7" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G19" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H19" s="7"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H19" s="7" t="inlineStr">
+        <is>
+          <t>3500614211</t>
+        </is>
+      </c>
+      <c r="I19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN KHOA HỌC CÔNG NGHỆ VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="J19" s="6" t="inlineStr">
+        <is>
+          <t>Số 6 đường 3 tháng 2, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K19" s="6"/>
       <c r="L19" s="13" t="n">
-        <v>768519.0</v>
+        <v>2056628.0</v>
       </c>
       <c r="M19" s="13" t="n">
-        <v>61481.0</v>
+        <v>164530.0</v>
       </c>
       <c r="N19" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O19" s="13" t="n">
-        <v>830000.0</v>
+        <v>2221158.0</v>
       </c>
       <c r="P19" s="6" t="inlineStr">
         <is>
@@ -1106,44 +1250,56 @@
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D20" s="7" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>774</t>
         </is>
       </c>
       <c r="E20" s="7" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>04/10/2025</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H20" s="7"/>
-      <c r="I20" s="6"/>
-      <c r="J20" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H20" s="7" t="inlineStr">
+        <is>
+          <t>0305148138</t>
+        </is>
+      </c>
+      <c r="I20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN ĐỊA VẬT LÝ GIẾNG KHOAN DẦU KHÍ</t>
+        </is>
+      </c>
+      <c r="J20" s="6" t="inlineStr">
+        <is>
+          <t>Tầng 4, Tòa nhà PVFCCo, Số 43 Mạc Đĩnh Chi, Phường Sài Gòn, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K20" s="6"/>
       <c r="L20" s="13" t="n">
-        <v>564815.0</v>
+        <v>2778674.0</v>
       </c>
       <c r="M20" s="13" t="n">
-        <v>45185.0</v>
+        <v>222294.0</v>
       </c>
       <c r="N20" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O20" s="13" t="n">
-        <v>610000.0</v>
+        <v>3000968.0</v>
       </c>
       <c r="P20" s="6" t="inlineStr">
         <is>
@@ -1167,44 +1323,56 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D21" s="7" t="inlineStr">
         <is>
-          <t>295</t>
+          <t>775</t>
         </is>
       </c>
       <c r="E21" s="7" t="inlineStr">
         <is>
-          <t>07/10/2025</t>
+          <t>04/10/2025</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G21" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H21" s="7"/>
-      <c r="I21" s="6"/>
-      <c r="J21" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H21" s="7" t="inlineStr">
+        <is>
+          <t>0100112437-005</t>
+        </is>
+      </c>
+      <c r="I21" s="6" t="inlineStr">
+        <is>
+          <t>NGÂN HÀNG TMCP NGOẠI THƯƠNG VIỆT NAM - CHI NHÁNH VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J21" s="6" t="inlineStr">
+        <is>
+          <t>27 Trần Hưng Đạo, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K21" s="6"/>
       <c r="L21" s="13" t="n">
-        <v>935186.0</v>
+        <v>7320301.0</v>
       </c>
       <c r="M21" s="13" t="n">
-        <v>74814.0</v>
+        <v>585624.0</v>
       </c>
       <c r="N21" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O21" s="13" t="n">
-        <v>1010000.0</v>
+        <v>7905925.0</v>
       </c>
       <c r="P21" s="6" t="inlineStr">
         <is>
@@ -1228,44 +1396,56 @@
       </c>
       <c r="C22" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D22" s="7" t="inlineStr">
         <is>
-          <t>296</t>
+          <t>776</t>
         </is>
       </c>
       <c r="E22" s="7" t="inlineStr">
         <is>
-          <t>08/10/2025</t>
+          <t>05/10/2025</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H22" s="7"/>
-      <c r="I22" s="6"/>
-      <c r="J22" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H22" s="7" t="inlineStr">
+        <is>
+          <t>0200124891</t>
+        </is>
+      </c>
+      <c r="I22" s="6" t="inlineStr">
+        <is>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN HÀNG HẢI VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="J22" s="6" t="inlineStr">
+        <is>
+          <t>Số 54A Nguyễn Chí Thanh, Phường Láng, Thành phố Hà Nội, Việt Nam</t>
+        </is>
+      </c>
       <c r="K22" s="6"/>
       <c r="L22" s="13" t="n">
-        <v>814815.0</v>
+        <v>951805.0</v>
       </c>
       <c r="M22" s="13" t="n">
-        <v>65185.0</v>
+        <v>76144.0</v>
       </c>
       <c r="N22" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O22" s="13" t="n">
-        <v>880000.0</v>
+        <v>1027949.0</v>
       </c>
       <c r="P22" s="6" t="inlineStr">
         <is>
@@ -1289,44 +1469,56 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D23" s="7" t="inlineStr">
         <is>
-          <t>297</t>
+          <t>777</t>
         </is>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
-          <t>08/10/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G23" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H23" s="7"/>
-      <c r="I23" s="6"/>
-      <c r="J23" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H23" s="7" t="inlineStr">
+        <is>
+          <t>3500820133</t>
+        </is>
+      </c>
+      <c r="I23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH DỊCH VỤ HÀNG HẢI VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J23" s="6" t="inlineStr">
+        <is>
+          <t>Số 40/16 Phan Đăng Lưu, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K23" s="6"/>
       <c r="L23" s="13" t="n">
-        <v>787037.0</v>
+        <v>855000.0</v>
       </c>
       <c r="M23" s="13" t="n">
-        <v>62963.0</v>
+        <v>85500.0</v>
       </c>
       <c r="N23" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O23" s="13" t="n">
-        <v>850000.0</v>
+        <v>940500.0</v>
       </c>
       <c r="P23" s="6" t="inlineStr">
         <is>
@@ -1350,44 +1542,56 @@
       </c>
       <c r="C24" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D24" s="7" t="inlineStr">
         <is>
-          <t>298</t>
+          <t>778</t>
         </is>
       </c>
       <c r="E24" s="7" t="inlineStr">
         <is>
-          <t>09/10/2025</t>
+          <t>06/10/2025</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H24" s="7"/>
-      <c r="I24" s="6"/>
-      <c r="J24" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H24" s="7" t="inlineStr">
+        <is>
+          <t>3500820133</t>
+        </is>
+      </c>
+      <c r="I24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH DỊCH VỤ HÀNG HẢI VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J24" s="6" t="inlineStr">
+        <is>
+          <t>Số 40/16 Phan Đăng Lưu, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K24" s="6"/>
       <c r="L24" s="13" t="n">
-        <v>967594.0</v>
+        <v>1128082.0</v>
       </c>
       <c r="M24" s="13" t="n">
-        <v>77406.0</v>
+        <v>90247.0</v>
       </c>
       <c r="N24" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O24" s="13" t="n">
-        <v>1045000.0</v>
+        <v>1218329.0</v>
       </c>
       <c r="P24" s="6" t="inlineStr">
         <is>
@@ -1411,44 +1615,56 @@
       </c>
       <c r="C25" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D25" s="7" t="inlineStr">
         <is>
-          <t>299</t>
+          <t>779</t>
         </is>
       </c>
       <c r="E25" s="7" t="inlineStr">
         <is>
-          <t>09/10/2025</t>
+          <t>07/10/2025</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G25" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H25" s="7"/>
-      <c r="I25" s="6"/>
-      <c r="J25" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H25" s="7" t="inlineStr">
+        <is>
+          <t>5800537716</t>
+        </is>
+      </c>
+      <c r="I25" s="6" t="inlineStr">
+        <is>
+          <t>TRUNG TÂM ỨNG DỤNG KỸ THUẬT HẠT NHÂN TRONG CÔNG NGHIỆP</t>
+        </is>
+      </c>
+      <c r="J25" s="6" t="inlineStr">
+        <is>
+          <t>Số 01, đường ĐT 723, Phường Lâm Viên - Đà Lạt, Lâm Đồng, Việt Nam</t>
+        </is>
+      </c>
       <c r="K25" s="6"/>
       <c r="L25" s="13" t="n">
-        <v>740740.0</v>
+        <v>2769896.0</v>
       </c>
       <c r="M25" s="13" t="n">
-        <v>59260.0</v>
+        <v>221592.0</v>
       </c>
       <c r="N25" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O25" s="13" t="n">
-        <v>800000.0</v>
+        <v>2991488.0</v>
       </c>
       <c r="P25" s="6" t="inlineStr">
         <is>
@@ -1472,44 +1688,56 @@
       </c>
       <c r="C26" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D26" s="7" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>780</t>
         </is>
       </c>
       <c r="E26" s="7" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>08/10/2025</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H26" s="7"/>
-      <c r="I26" s="6"/>
-      <c r="J26" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H26" s="7" t="inlineStr">
+        <is>
+          <t>3501881097</t>
+        </is>
+      </c>
+      <c r="I26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN CƠ KHÍ HÀNG HẢI MIỀN NAM</t>
+        </is>
+      </c>
+      <c r="J26" s="6" t="inlineStr">
+        <is>
+          <t>Số 847/15 đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K26" s="6"/>
       <c r="L26" s="13" t="n">
-        <v>744782.0</v>
+        <v>6380616.0</v>
       </c>
       <c r="M26" s="13" t="n">
-        <v>60218.0</v>
+        <v>510449.0</v>
       </c>
       <c r="N26" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O26" s="13" t="n">
-        <v>805000.0</v>
+        <v>6891065.0</v>
       </c>
       <c r="P26" s="6" t="inlineStr">
         <is>
@@ -1533,44 +1761,56 @@
       </c>
       <c r="C27" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D27" s="7" t="inlineStr">
         <is>
-          <t>301</t>
+          <t>781</t>
         </is>
       </c>
       <c r="E27" s="7" t="inlineStr">
         <is>
-          <t>10/10/2025</t>
+          <t>08/10/2025</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G27" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H27" s="7"/>
-      <c r="I27" s="6"/>
-      <c r="J27" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H27" s="7" t="inlineStr">
+        <is>
+          <t>0100110768-023</t>
+        </is>
+      </c>
+      <c r="I27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY BẢO HIỂM PJICO VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J27" s="6" t="inlineStr">
+        <is>
+          <t>70 Cô Giang, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K27" s="6"/>
       <c r="L27" s="13" t="n">
-        <v>907407.0</v>
+        <v>963592.0</v>
       </c>
       <c r="M27" s="13" t="n">
-        <v>72593.0</v>
+        <v>77087.0</v>
       </c>
       <c r="N27" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O27" s="13" t="n">
-        <v>980000.0</v>
+        <v>1040679.0</v>
       </c>
       <c r="P27" s="6" t="inlineStr">
         <is>
@@ -1594,44 +1834,52 @@
       </c>
       <c r="C28" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D28" s="7" t="inlineStr">
         <is>
-          <t>302</t>
+          <t>782</t>
         </is>
       </c>
       <c r="E28" s="7" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>08/10/2025</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="H28" s="7"/>
-      <c r="I28" s="6"/>
-      <c r="J28" s="6"/>
+      <c r="I28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG ĐOÀN CÔNG TY ĐIỀU HÀNH DẦU KHÍ PHÚ QUỐC</t>
+        </is>
+      </c>
+      <c r="J28" s="6" t="inlineStr">
+        <is>
+          <t>Tầng 25, Tòa nhà Vietcombank, số 5 Công trường Mê Linh, Phường Sài Gòn, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K28" s="6"/>
       <c r="L28" s="13" t="n">
-        <v>1037038.0</v>
+        <v>4583813.0</v>
       </c>
       <c r="M28" s="13" t="n">
-        <v>82962.0</v>
+        <v>366705.0</v>
       </c>
       <c r="N28" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O28" s="13" t="n">
-        <v>1120000.0</v>
+        <v>4950518.0</v>
       </c>
       <c r="P28" s="6" t="inlineStr">
         <is>
@@ -1655,44 +1903,56 @@
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D29" s="7" t="inlineStr">
         <is>
-          <t>303</t>
+          <t>783</t>
         </is>
       </c>
       <c r="E29" s="7" t="inlineStr">
         <is>
-          <t>11/10/2025</t>
+          <t>09/10/2025</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G29" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H29" s="7"/>
-      <c r="I29" s="6"/>
-      <c r="J29" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H29" s="7" t="inlineStr">
+        <is>
+          <t>1800278630</t>
+        </is>
+      </c>
+      <c r="I29" s="6" t="inlineStr">
+        <is>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN SÀI GÒN - HÀ NỘI</t>
+        </is>
+      </c>
+      <c r="J29" s="6" t="inlineStr">
+        <is>
+          <t>Số 77, Phố Trần Hưng Đạo, Phường Cửa Nam, Thành Phố Hà Nội, Việt Nam</t>
+        </is>
+      </c>
       <c r="K29" s="6"/>
       <c r="L29" s="13" t="n">
-        <v>1101851.0</v>
+        <v>9556032.0</v>
       </c>
       <c r="M29" s="13" t="n">
-        <v>88149.0</v>
+        <v>764483.0</v>
       </c>
       <c r="N29" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O29" s="13" t="n">
-        <v>1190000.0</v>
+        <v>1.0320515E7</v>
       </c>
       <c r="P29" s="6" t="inlineStr">
         <is>
@@ -1716,44 +1976,56 @@
       </c>
       <c r="C30" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D30" s="7" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>784</t>
         </is>
       </c>
       <c r="E30" s="7" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>09/10/2025</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G30" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H30" s="7"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H30" s="7" t="inlineStr">
+        <is>
+          <t>3502530158</t>
+        </is>
+      </c>
+      <c r="I30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ VẬN TẢI DU LỊCH XUÂN THẮNG</t>
+        </is>
+      </c>
+      <c r="J30" s="6" t="inlineStr">
+        <is>
+          <t>112/24 Đường Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K30" s="6"/>
       <c r="L30" s="13" t="n">
-        <v>879629.0</v>
+        <v>1152000.0</v>
       </c>
       <c r="M30" s="13" t="n">
-        <v>70371.0</v>
+        <v>115200.0</v>
       </c>
       <c r="N30" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O30" s="13" t="n">
-        <v>950000.0</v>
+        <v>1267200.0</v>
       </c>
       <c r="P30" s="6" t="inlineStr">
         <is>
@@ -1777,44 +2049,56 @@
       </c>
       <c r="C31" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D31" s="7" t="inlineStr">
         <is>
-          <t>305</t>
+          <t>785</t>
         </is>
       </c>
       <c r="E31" s="7" t="inlineStr">
         <is>
-          <t>12/10/2025</t>
+          <t>09/10/2025</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G31" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H31" s="7"/>
-      <c r="I31" s="6"/>
-      <c r="J31" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H31" s="7" t="inlineStr">
+        <is>
+          <t>3502530158</t>
+        </is>
+      </c>
+      <c r="I31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN THƯƠNG MẠI DỊCH VỤ VẬN TẢI DU LỊCH XUÂN THẮNG</t>
+        </is>
+      </c>
+      <c r="J31" s="6" t="inlineStr">
+        <is>
+          <t>112/24 Đường Đô Lương, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K31" s="6"/>
       <c r="L31" s="13" t="n">
-        <v>916666.0</v>
+        <v>2500704.0</v>
       </c>
       <c r="M31" s="13" t="n">
-        <v>73334.0</v>
+        <v>200056.0</v>
       </c>
       <c r="N31" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O31" s="13" t="n">
-        <v>990000.0</v>
+        <v>2700760.0</v>
       </c>
       <c r="P31" s="6" t="inlineStr">
         <is>
@@ -1838,44 +2122,56 @@
       </c>
       <c r="C32" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D32" s="7" t="inlineStr">
         <is>
-          <t>306</t>
+          <t>786</t>
         </is>
       </c>
       <c r="E32" s="7" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>09/10/2025</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H32" s="7"/>
-      <c r="I32" s="6"/>
-      <c r="J32" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H32" s="7" t="inlineStr">
+        <is>
+          <t>3500614211</t>
+        </is>
+      </c>
+      <c r="I32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN KHOA HỌC CÔNG NGHỆ VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="J32" s="6" t="inlineStr">
+        <is>
+          <t>Số 6 đường 3 tháng 2, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K32" s="6"/>
       <c r="L32" s="13" t="n">
-        <v>682407.0</v>
+        <v>2778209.0</v>
       </c>
       <c r="M32" s="13" t="n">
-        <v>54593.0</v>
+        <v>222257.0</v>
       </c>
       <c r="N32" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O32" s="13" t="n">
-        <v>737000.0</v>
+        <v>3000466.0</v>
       </c>
       <c r="P32" s="6" t="inlineStr">
         <is>
@@ -1899,44 +2195,56 @@
       </c>
       <c r="C33" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D33" s="7" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>787</t>
         </is>
       </c>
       <c r="E33" s="7" t="inlineStr">
         <is>
-          <t>13/10/2025</t>
+          <t>09/10/2025</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G33" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H33" s="7"/>
-      <c r="I33" s="6"/>
-      <c r="J33" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H33" s="7" t="inlineStr">
+        <is>
+          <t>3501881097</t>
+        </is>
+      </c>
+      <c r="I33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN CƠ KHÍ HÀNG HẢI MIỀN NAM</t>
+        </is>
+      </c>
+      <c r="J33" s="6" t="inlineStr">
+        <is>
+          <t>Số 847/15 đường 30/4, Phường Phước Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K33" s="6"/>
       <c r="L33" s="13" t="n">
-        <v>1037038.0</v>
+        <v>5266710.0</v>
       </c>
       <c r="M33" s="13" t="n">
-        <v>82962.0</v>
+        <v>421337.0</v>
       </c>
       <c r="N33" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O33" s="13" t="n">
-        <v>1120000.0</v>
+        <v>5688047.0</v>
       </c>
       <c r="P33" s="6" t="inlineStr">
         <is>
@@ -1960,44 +2268,56 @@
       </c>
       <c r="C34" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D34" s="7" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>788</t>
         </is>
       </c>
       <c r="E34" s="7" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H34" s="7"/>
-      <c r="I34" s="6"/>
-      <c r="J34" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H34" s="7" t="inlineStr">
+        <is>
+          <t>3500815711</t>
+        </is>
+      </c>
+      <c r="I34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN CẤP NƯỚC TÓC TIÊN</t>
+        </is>
+      </c>
+      <c r="J34" s="6" t="inlineStr">
+        <is>
+          <t>Ấp 6, Xã Châu Pha, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K34" s="6"/>
       <c r="L34" s="13" t="n">
-        <v>925926.0</v>
+        <v>1623571.0</v>
       </c>
       <c r="M34" s="13" t="n">
-        <v>74074.0</v>
+        <v>129886.0</v>
       </c>
       <c r="N34" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O34" s="13" t="n">
-        <v>1000000.0</v>
+        <v>1753457.0</v>
       </c>
       <c r="P34" s="6" t="inlineStr">
         <is>
@@ -2021,44 +2341,56 @@
       </c>
       <c r="C35" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D35" s="7" t="inlineStr">
         <is>
-          <t>309</t>
+          <t>789</t>
         </is>
       </c>
       <c r="E35" s="7" t="inlineStr">
         <is>
-          <t>14/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G35" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H35" s="7"/>
-      <c r="I35" s="6"/>
-      <c r="J35" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H35" s="7" t="inlineStr">
+        <is>
+          <t>0303165480-011</t>
+        </is>
+      </c>
+      <c r="I35" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY PHÂN BÓN VÀ HÓA CHẤT DẦU KHÍ - CÔNG TY CỔ PHẦN - TRUNG TÂM NGHIÊN CỨU VÀ ỨNG DỤNG</t>
+        </is>
+      </c>
+      <c r="J35" s="6" t="inlineStr">
+        <is>
+          <t>Khu công nghiệp Phú Mỹ I, Phường Phú Mỹ, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K35" s="6"/>
       <c r="L35" s="13" t="n">
-        <v>462963.0</v>
+        <v>1597945.0</v>
       </c>
       <c r="M35" s="13" t="n">
-        <v>37037.0</v>
+        <v>127836.0</v>
       </c>
       <c r="N35" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O35" s="13" t="n">
-        <v>500000.0</v>
+        <v>1725781.0</v>
       </c>
       <c r="P35" s="6" t="inlineStr">
         <is>
@@ -2082,44 +2414,56 @@
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D36" s="7" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>790</t>
         </is>
       </c>
       <c r="E36" s="7" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G36" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H36" s="7"/>
-      <c r="I36" s="6"/>
-      <c r="J36" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H36" s="7" t="inlineStr">
+        <is>
+          <t>0101335193-028</t>
+        </is>
+      </c>
+      <c r="I36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY BẢO HIỂM VIETINBANK VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J36" s="6" t="inlineStr">
+        <is>
+          <t>Số 19 Phạm Ngọc Thạch, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K36" s="6"/>
       <c r="L36" s="13" t="n">
-        <v>163637.0</v>
+        <v>4370521.0</v>
       </c>
       <c r="M36" s="13" t="n">
-        <v>16363.0</v>
+        <v>349642.0</v>
       </c>
       <c r="N36" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O36" s="13" t="n">
-        <v>180000.0</v>
+        <v>4720163.0</v>
       </c>
       <c r="P36" s="6" t="inlineStr">
         <is>
@@ -2143,44 +2487,56 @@
       </c>
       <c r="C37" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D37" s="7" t="inlineStr">
         <is>
-          <t>311</t>
+          <t>791</t>
         </is>
       </c>
       <c r="E37" s="7" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>10/10/2025</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G37" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H37" s="7"/>
-      <c r="I37" s="6"/>
-      <c r="J37" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H37" s="7" t="inlineStr">
+        <is>
+          <t>1800278630</t>
+        </is>
+      </c>
+      <c r="I37" s="6" t="inlineStr">
+        <is>
+          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN SÀI GÒN - HÀ NỘI</t>
+        </is>
+      </c>
+      <c r="J37" s="6" t="inlineStr">
+        <is>
+          <t>Số 77, Phố Trần Hưng Đạo, Phường Cửa Nam, Thành Phố Hà Nội, Việt Nam</t>
+        </is>
+      </c>
       <c r="K37" s="6"/>
       <c r="L37" s="13" t="n">
-        <v>657407.0</v>
+        <v>1.2639647E7</v>
       </c>
       <c r="M37" s="13" t="n">
-        <v>52593.0</v>
+        <v>1011172.0</v>
       </c>
       <c r="N37" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O37" s="13" t="n">
-        <v>710000.0</v>
+        <v>1.3650819E7</v>
       </c>
       <c r="P37" s="6" t="inlineStr">
         <is>
@@ -2204,44 +2560,56 @@
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D38" s="7" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>792</t>
         </is>
       </c>
       <c r="E38" s="7" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H38" s="7"/>
-      <c r="I38" s="6"/>
-      <c r="J38" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H38" s="7" t="inlineStr">
+        <is>
+          <t>0303625152</t>
+        </is>
+      </c>
+      <c r="I38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH DU LỊCH - DỊCH VỤ VÀ THƯƠNG MẠI SEN VIỆT</t>
+        </is>
+      </c>
+      <c r="J38" s="6" t="inlineStr">
+        <is>
+          <t>85 Điện Biên Phủ, Phường Tân Định, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K38" s="6"/>
       <c r="L38" s="13" t="n">
-        <v>129629.0</v>
+        <v>884082.0</v>
       </c>
       <c r="M38" s="13" t="n">
-        <v>10371.0</v>
+        <v>70727.0</v>
       </c>
       <c r="N38" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O38" s="13" t="n">
-        <v>140000.0</v>
+        <v>954809.0</v>
       </c>
       <c r="P38" s="6" t="inlineStr">
         <is>
@@ -2265,44 +2633,56 @@
       </c>
       <c r="C39" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D39" s="7" t="inlineStr">
         <is>
-          <t>313</t>
+          <t>793</t>
         </is>
       </c>
       <c r="E39" s="7" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G39" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H39" s="7"/>
-      <c r="I39" s="6"/>
-      <c r="J39" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H39" s="7" t="inlineStr">
+        <is>
+          <t>3502390542</t>
+        </is>
+      </c>
+      <c r="I39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TƯ VẤN KIẾN TRÚC VÀ XÂY DỰNG IDA</t>
+        </is>
+      </c>
+      <c r="J39" s="6" t="inlineStr">
+        <is>
+          <t>266/10A22 Lê Lợi, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K39" s="6"/>
       <c r="L39" s="13" t="n">
-        <v>83333.0</v>
+        <v>603484.0</v>
       </c>
       <c r="M39" s="13" t="n">
-        <v>6667.0</v>
+        <v>48279.0</v>
       </c>
       <c r="N39" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O39" s="13" t="n">
-        <v>90000.0</v>
+        <v>651763.0</v>
       </c>
       <c r="P39" s="6" t="inlineStr">
         <is>
@@ -2326,44 +2706,56 @@
       </c>
       <c r="C40" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>314</t>
+          <t>794</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H40" s="7"/>
-      <c r="I40" s="6"/>
-      <c r="J40" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H40" s="7" t="inlineStr">
+        <is>
+          <t>3502390542</t>
+        </is>
+      </c>
+      <c r="I40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH TƯ VẤN KIẾN TRÚC VÀ XÂY DỰNG IDA</t>
+        </is>
+      </c>
+      <c r="J40" s="6" t="inlineStr">
+        <is>
+          <t>266/10A22 Lê Lợi, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K40" s="6"/>
       <c r="L40" s="13" t="n">
-        <v>1027777.0</v>
+        <v>540000.0</v>
       </c>
       <c r="M40" s="13" t="n">
-        <v>82223.0</v>
+        <v>54000.0</v>
       </c>
       <c r="N40" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O40" s="13" t="n">
-        <v>1110000.0</v>
+        <v>594000.0</v>
       </c>
       <c r="P40" s="6" t="inlineStr">
         <is>
@@ -2387,44 +2779,56 @@
       </c>
       <c r="C41" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D41" s="7" t="inlineStr">
         <is>
-          <t>315</t>
+          <t>795</t>
         </is>
       </c>
       <c r="E41" s="7" t="inlineStr">
         <is>
-          <t>17/10/2025</t>
+          <t>11/10/2025</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G41" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H41" s="7"/>
-      <c r="I41" s="6"/>
-      <c r="J41" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H41" s="7" t="inlineStr">
+        <is>
+          <t>0100110768-023</t>
+        </is>
+      </c>
+      <c r="I41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY BẢO HIỂM PJICO VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J41" s="6" t="inlineStr">
+        <is>
+          <t>70 Cô Giang, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K41" s="6"/>
       <c r="L41" s="13" t="n">
-        <v>369361.0</v>
+        <v>1951333.0</v>
       </c>
       <c r="M41" s="13" t="n">
-        <v>30639.0</v>
+        <v>156107.0</v>
       </c>
       <c r="N41" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O41" s="13" t="n">
-        <v>400000.0</v>
+        <v>2107440.0</v>
       </c>
       <c r="P41" s="6" t="inlineStr">
         <is>
@@ -2448,44 +2852,56 @@
       </c>
       <c r="C42" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D42" s="7" t="inlineStr">
         <is>
-          <t>316</t>
+          <t>796</t>
         </is>
       </c>
       <c r="E42" s="7" t="inlineStr">
         <is>
-          <t>18/10/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H42" s="7"/>
-      <c r="I42" s="6"/>
-      <c r="J42" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H42" s="7" t="inlineStr">
+        <is>
+          <t>3500690389</t>
+        </is>
+      </c>
+      <c r="I42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI - DỊCH VỤ - XÂY DỰNG SAO BIỂN</t>
+        </is>
+      </c>
+      <c r="J42" s="6" t="inlineStr">
+        <is>
+          <t>Số 15 Lô G1 - Trung tâm thương mại, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K42" s="6"/>
       <c r="L42" s="13" t="n">
-        <v>833333.0</v>
+        <v>1418172.0</v>
       </c>
       <c r="M42" s="13" t="n">
-        <v>66667.0</v>
+        <v>113454.0</v>
       </c>
       <c r="N42" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O42" s="13" t="n">
-        <v>900000.0</v>
+        <v>1531626.0</v>
       </c>
       <c r="P42" s="6" t="inlineStr">
         <is>
@@ -2509,44 +2925,56 @@
       </c>
       <c r="C43" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D43" s="7" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>797</t>
         </is>
       </c>
       <c r="E43" s="7" t="inlineStr">
         <is>
-          <t>18/10/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G43" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H43" s="7"/>
-      <c r="I43" s="6"/>
-      <c r="J43" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H43" s="7" t="inlineStr">
+        <is>
+          <t>3502465491</t>
+        </is>
+      </c>
+      <c r="I43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ VẬT TƯ Y TẾ THỦY TIÊN</t>
+        </is>
+      </c>
+      <c r="J43" s="6" t="inlineStr">
+        <is>
+          <t>Số 412/29 Lê Hồng Phong, Phường Vũng Tàu , Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
       <c r="K43" s="6"/>
       <c r="L43" s="13" t="n">
-        <v>166666.0</v>
+        <v>1044000.0</v>
       </c>
       <c r="M43" s="13" t="n">
-        <v>13334.0</v>
+        <v>104400.0</v>
       </c>
       <c r="N43" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O43" s="13" t="n">
-        <v>180000.0</v>
+        <v>1148400.0</v>
       </c>
       <c r="P43" s="6" t="inlineStr">
         <is>
@@ -2570,44 +2998,56 @@
       </c>
       <c r="C44" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D44" s="7" t="inlineStr">
         <is>
-          <t>318</t>
+          <t>798</t>
         </is>
       </c>
       <c r="E44" s="7" t="inlineStr">
         <is>
-          <t>18/10/2025</t>
+          <t>12/10/2025</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H44" s="7"/>
-      <c r="I44" s="6"/>
-      <c r="J44" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H44" s="7" t="inlineStr">
+        <is>
+          <t>3502465491</t>
+        </is>
+      </c>
+      <c r="I44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ VẬT TƯ Y TẾ THỦY TIÊN</t>
+        </is>
+      </c>
+      <c r="J44" s="6" t="inlineStr">
+        <is>
+          <t>Số 412/29 Lê Hồng Phong, Phường Vũng Tàu , Thành phố Hồ Chí Minh</t>
+        </is>
+      </c>
       <c r="K44" s="6"/>
       <c r="L44" s="13" t="n">
-        <v>694446.0</v>
+        <v>519796.0</v>
       </c>
       <c r="M44" s="13" t="n">
-        <v>55554.0</v>
+        <v>41584.0</v>
       </c>
       <c r="N44" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O44" s="13" t="n">
-        <v>750000.0</v>
+        <v>561380.0</v>
       </c>
       <c r="P44" s="6" t="inlineStr">
         <is>
@@ -2631,44 +3071,56 @@
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D45" s="7" t="inlineStr">
         <is>
-          <t>319</t>
+          <t>799</t>
         </is>
       </c>
       <c r="E45" s="7" t="inlineStr">
         <is>
-          <t>18/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G45" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H45" s="7"/>
-      <c r="I45" s="6"/>
-      <c r="J45" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H45" s="7" t="inlineStr">
+        <is>
+          <t>3500833615</t>
+        </is>
+      </c>
+      <c r="I45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XÂY LẮP ĐƯỜNG ỐNG BỂ CHỨA DẦU KHÍ</t>
+        </is>
+      </c>
+      <c r="J45" s="6" t="inlineStr">
+        <is>
+          <t>35G đường 30/4,Phường Tam Thắng,Thành phố Hồ Chí Minh,Việt Nam</t>
+        </is>
+      </c>
       <c r="K45" s="6"/>
       <c r="L45" s="13" t="n">
-        <v>90909.0</v>
+        <v>2486351.0</v>
       </c>
       <c r="M45" s="13" t="n">
-        <v>9091.0</v>
+        <v>198908.0</v>
       </c>
       <c r="N45" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O45" s="13" t="n">
-        <v>100000.0</v>
+        <v>2685259.0</v>
       </c>
       <c r="P45" s="6" t="inlineStr">
         <is>
@@ -2692,44 +3144,56 @@
       </c>
       <c r="C46" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D46" s="7" t="inlineStr">
         <is>
-          <t>320</t>
+          <t>800</t>
         </is>
       </c>
       <c r="E46" s="7" t="inlineStr">
         <is>
-          <t>18/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G46" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H46" s="7"/>
-      <c r="I46" s="6"/>
-      <c r="J46" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H46" s="7" t="inlineStr">
+        <is>
+          <t>3500101844-001</t>
+        </is>
+      </c>
+      <c r="I46" s="6" t="inlineStr">
+        <is>
+          <t>KHÁCH SẠN GRAND PALACE</t>
+        </is>
+      </c>
+      <c r="J46" s="6" t="inlineStr">
+        <is>
+          <t>Số 01 Nguyễn Trãi, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K46" s="6"/>
       <c r="L46" s="13" t="n">
-        <v>490741.0</v>
+        <v>1667895.0</v>
       </c>
       <c r="M46" s="13" t="n">
-        <v>39259.0</v>
+        <v>133432.0</v>
       </c>
       <c r="N46" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O46" s="13" t="n">
-        <v>530000.0</v>
+        <v>1801327.0</v>
       </c>
       <c r="P46" s="6" t="inlineStr">
         <is>
@@ -2753,44 +3217,56 @@
       </c>
       <c r="C47" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D47" s="7" t="inlineStr">
         <is>
-          <t>321</t>
+          <t>801</t>
         </is>
       </c>
       <c r="E47" s="7" t="inlineStr">
         <is>
-          <t>19/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G47" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H47" s="7"/>
-      <c r="I47" s="6"/>
-      <c r="J47" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H47" s="7" t="inlineStr">
+        <is>
+          <t>3500833615</t>
+        </is>
+      </c>
+      <c r="I47" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN XÂY LẮP ĐƯỜNG ỐNG BỂ CHỨA DẦU KHÍ</t>
+        </is>
+      </c>
+      <c r="J47" s="6" t="inlineStr">
+        <is>
+          <t>35G đường 30/4,Phường Tam Thắng,Thành phố Hồ Chí Minh,Việt Nam</t>
+        </is>
+      </c>
       <c r="K47" s="6"/>
       <c r="L47" s="13" t="n">
-        <v>319023.0</v>
+        <v>2975899.0</v>
       </c>
       <c r="M47" s="13" t="n">
-        <v>25977.0</v>
+        <v>238072.0</v>
       </c>
       <c r="N47" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O47" s="13" t="n">
-        <v>345000.0</v>
+        <v>3213971.0</v>
       </c>
       <c r="P47" s="6" t="inlineStr">
         <is>
@@ -2814,44 +3290,56 @@
       </c>
       <c r="C48" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D48" s="7" t="inlineStr">
         <is>
-          <t>322</t>
+          <t>802</t>
         </is>
       </c>
       <c r="E48" s="7" t="inlineStr">
         <is>
-          <t>19/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G48" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H48" s="7"/>
-      <c r="I48" s="6"/>
-      <c r="J48" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H48" s="7" t="inlineStr">
+        <is>
+          <t>3500513301</t>
+        </is>
+      </c>
+      <c r="I48" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG - THƯƠNG MẠI LANG PHONG</t>
+        </is>
+      </c>
+      <c r="J48" s="6" t="inlineStr">
+        <is>
+          <t>Số 200 Lý Tự Trọng,Phường Vũng Tàu,Thành phố Hồ Chí Minh,Việt Nam</t>
+        </is>
+      </c>
       <c r="K48" s="6"/>
       <c r="L48" s="13" t="n">
-        <v>892593.0</v>
+        <v>1080000.0</v>
       </c>
       <c r="M48" s="13" t="n">
-        <v>71407.0</v>
+        <v>108000.0</v>
       </c>
       <c r="N48" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O48" s="13" t="n">
-        <v>964000.0</v>
+        <v>1188000.0</v>
       </c>
       <c r="P48" s="6" t="inlineStr">
         <is>
@@ -2875,44 +3363,56 @@
       </c>
       <c r="C49" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D49" s="7" t="inlineStr">
         <is>
-          <t>323</t>
+          <t>803</t>
         </is>
       </c>
       <c r="E49" s="7" t="inlineStr">
         <is>
-          <t>19/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G49" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H49" s="7"/>
-      <c r="I49" s="6"/>
-      <c r="J49" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H49" s="7" t="inlineStr">
+        <is>
+          <t>3500513301</t>
+        </is>
+      </c>
+      <c r="I49" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH XÂY DỰNG - THƯƠNG MẠI LANG PHONG</t>
+        </is>
+      </c>
+      <c r="J49" s="6" t="inlineStr">
+        <is>
+          <t>Số 200 Lý Tự Trọng,Phường Vũng Tàu,Thành phố Hồ Chí Minh,Việt Nam</t>
+        </is>
+      </c>
       <c r="K49" s="6"/>
       <c r="L49" s="13" t="n">
-        <v>1055555.0</v>
+        <v>286648.0</v>
       </c>
       <c r="M49" s="13" t="n">
-        <v>84445.0</v>
+        <v>22932.0</v>
       </c>
       <c r="N49" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O49" s="13" t="n">
-        <v>1140000.0</v>
+        <v>309580.0</v>
       </c>
       <c r="P49" s="6" t="inlineStr">
         <is>
@@ -2936,44 +3436,56 @@
       </c>
       <c r="C50" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D50" s="7" t="inlineStr">
         <is>
-          <t>324</t>
+          <t>804</t>
         </is>
       </c>
       <c r="E50" s="7" t="inlineStr">
         <is>
-          <t>19/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H50" s="7"/>
-      <c r="I50" s="6"/>
-      <c r="J50" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H50" s="7" t="inlineStr">
+        <is>
+          <t>3502182119</t>
+        </is>
+      </c>
+      <c r="I50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN DỊCH VỤ KỸ THUẬT NPL</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
+          <t>Số 18 K3, Trung tâm thương mại, Phường Tam Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K50" s="6"/>
       <c r="L50" s="13" t="n">
-        <v>294108.0</v>
+        <v>1038186.0</v>
       </c>
       <c r="M50" s="13" t="n">
-        <v>23892.0</v>
+        <v>83055.0</v>
       </c>
       <c r="N50" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O50" s="13" t="n">
-        <v>318000.0</v>
+        <v>1121241.0</v>
       </c>
       <c r="P50" s="6" t="inlineStr">
         <is>
@@ -2997,44 +3509,56 @@
       </c>
       <c r="C51" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D51" s="7" t="inlineStr">
         <is>
-          <t>325</t>
+          <t>805</t>
         </is>
       </c>
       <c r="E51" s="7" t="inlineStr">
         <is>
-          <t>19/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G51" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H51" s="7"/>
-      <c r="I51" s="6"/>
-      <c r="J51" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H51" s="7" t="inlineStr">
+        <is>
+          <t>3500707730</t>
+        </is>
+      </c>
+      <c r="I51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ PHÁT TRIỂN - XÂY DỰNG (DIC) SỐ 2</t>
+        </is>
+      </c>
+      <c r="J51" s="6" t="inlineStr">
+        <is>
+          <t>Số 5 đường số 6 Khu đô thị Chí Linh, Phường Rạch Dừa, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K51" s="6"/>
       <c r="L51" s="13" t="n">
-        <v>92593.0</v>
+        <v>7166649.0</v>
       </c>
       <c r="M51" s="13" t="n">
-        <v>7407.0</v>
+        <v>573332.0</v>
       </c>
       <c r="N51" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O51" s="13" t="n">
-        <v>100000.0</v>
+        <v>7739981.0</v>
       </c>
       <c r="P51" s="6" t="inlineStr">
         <is>
@@ -3058,27 +3582,27 @@
       </c>
       <c r="C52" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D52" s="7" t="inlineStr">
         <is>
-          <t>326</t>
+          <t>806</t>
         </is>
       </c>
       <c r="E52" s="7" t="inlineStr">
         <is>
-          <t>19/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G52" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="H52" s="7"/>
@@ -3086,16 +3610,16 @@
       <c r="J52" s="6"/>
       <c r="K52" s="6"/>
       <c r="L52" s="13" t="n">
-        <v>222222.0</v>
+        <v>670000.0</v>
       </c>
       <c r="M52" s="13" t="n">
-        <v>17778.0</v>
+        <v>53600.0</v>
       </c>
       <c r="N52" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O52" s="13" t="n">
-        <v>240000.0</v>
+        <v>723600.0</v>
       </c>
       <c r="P52" s="6" t="inlineStr">
         <is>
@@ -3119,27 +3643,27 @@
       </c>
       <c r="C53" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D53" s="7" t="inlineStr">
         <is>
-          <t>327</t>
+          <t>807</t>
         </is>
       </c>
       <c r="E53" s="7" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>13/10/2025</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G53" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="H53" s="7"/>
@@ -3147,16 +3671,16 @@
       <c r="J53" s="6"/>
       <c r="K53" s="6"/>
       <c r="L53" s="13" t="n">
-        <v>636110.0</v>
+        <v>1044000.0</v>
       </c>
       <c r="M53" s="13" t="n">
-        <v>50890.0</v>
+        <v>104400.0</v>
       </c>
       <c r="N53" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O53" s="13" t="n">
-        <v>687000.0</v>
+        <v>1148400.0</v>
       </c>
       <c r="P53" s="6" t="inlineStr">
         <is>
@@ -3180,44 +3704,56 @@
       </c>
       <c r="C54" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D54" s="7" t="inlineStr">
         <is>
-          <t>328</t>
+          <t>808</t>
         </is>
       </c>
       <c r="E54" s="7" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="F54" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G54" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H54" s="7"/>
-      <c r="I54" s="6"/>
-      <c r="J54" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H54" s="7" t="inlineStr">
+        <is>
+          <t>0101057919-016</t>
+        </is>
+      </c>
+      <c r="I54" s="6" t="inlineStr">
+        <is>
+          <t>Ngân Hàng TMCP Đại Chúng Việt Nam - Chi nhánh Bà Rịa Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="J54" s="6" t="inlineStr">
+        <is>
+          <t>Số 01 Lý Tự Trọng, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K54" s="6"/>
       <c r="L54" s="13" t="n">
-        <v>333333.0</v>
+        <v>930815.0</v>
       </c>
       <c r="M54" s="13" t="n">
-        <v>26667.0</v>
+        <v>74465.0</v>
       </c>
       <c r="N54" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O54" s="13" t="n">
-        <v>360000.0</v>
+        <v>1005280.0</v>
       </c>
       <c r="P54" s="6" t="inlineStr">
         <is>
@@ -3241,44 +3777,56 @@
       </c>
       <c r="C55" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D55" s="7" t="inlineStr">
         <is>
-          <t>329</t>
+          <t>809</t>
         </is>
       </c>
       <c r="E55" s="7" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="F55" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G55" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H55" s="7"/>
-      <c r="I55" s="6"/>
-      <c r="J55" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H55" s="7" t="inlineStr">
+        <is>
+          <t>0101335193-028</t>
+        </is>
+      </c>
+      <c r="I55" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY BẢO HIỂM VIETINBANK VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J55" s="6" t="inlineStr">
+        <is>
+          <t>Số 19 Phạm Ngọc Thạch, Phường Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K55" s="6"/>
       <c r="L55" s="13" t="n">
-        <v>240741.0</v>
+        <v>4576510.0</v>
       </c>
       <c r="M55" s="13" t="n">
-        <v>19259.0</v>
+        <v>366121.0</v>
       </c>
       <c r="N55" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O55" s="13" t="n">
-        <v>260000.0</v>
+        <v>4942631.0</v>
       </c>
       <c r="P55" s="6" t="inlineStr">
         <is>
@@ -3302,27 +3850,27 @@
       </c>
       <c r="C56" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D56" s="7" t="inlineStr">
         <is>
-          <t>330</t>
+          <t>810</t>
         </is>
       </c>
       <c r="E56" s="7" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="F56" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G56" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
         </is>
       </c>
       <c r="H56" s="7"/>
@@ -3330,16 +3878,16 @@
       <c r="J56" s="6"/>
       <c r="K56" s="6"/>
       <c r="L56" s="13" t="n">
-        <v>388889.0</v>
+        <v>348000.0</v>
       </c>
       <c r="M56" s="13" t="n">
-        <v>31111.0</v>
+        <v>27840.0</v>
       </c>
       <c r="N56" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O56" s="13" t="n">
-        <v>420000.0</v>
+        <v>375840.0</v>
       </c>
       <c r="P56" s="6" t="inlineStr">
         <is>
@@ -3363,44 +3911,56 @@
       </c>
       <c r="C57" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D57" s="7" t="inlineStr">
         <is>
-          <t>331</t>
+          <t>811</t>
         </is>
       </c>
       <c r="E57" s="7" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>14/10/2025</t>
         </is>
       </c>
       <c r="F57" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G57" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H57" s="7"/>
-      <c r="I57" s="6"/>
-      <c r="J57" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H57" s="7" t="inlineStr">
+        <is>
+          <t>0100109120-008</t>
+        </is>
+      </c>
+      <c r="I57" s="6" t="inlineStr">
+        <is>
+          <t>CHI CỤC ĐĂNG KIỂM SỐ 9</t>
+        </is>
+      </c>
+      <c r="J57" s="6" t="inlineStr">
+        <is>
+          <t>Số 102 Xô Viết Nghệ Tĩnh, Phường Vũng Tàu, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
       <c r="K57" s="6"/>
       <c r="L57" s="13" t="n">
-        <v>513889.0</v>
+        <v>4445600.0</v>
       </c>
       <c r="M57" s="13" t="n">
-        <v>41111.0</v>
+        <v>355648.0</v>
       </c>
       <c r="N57" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O57" s="13" t="n">
-        <v>555000.0</v>
+        <v>4801248.0</v>
       </c>
       <c r="P57" s="6" t="inlineStr">
         <is>
@@ -3424,44 +3984,56 @@
       </c>
       <c r="C58" s="6" t="inlineStr">
         <is>
-          <t>C25MYY</t>
+          <t>C25MVP</t>
         </is>
       </c>
       <c r="D58" s="7" t="inlineStr">
         <is>
-          <t>332</t>
+          <t>812</t>
         </is>
       </c>
       <c r="E58" s="7" t="inlineStr">
         <is>
-          <t>20/10/2025</t>
+          <t>15/10/2025</t>
         </is>
       </c>
       <c r="F58" s="7" t="inlineStr">
         <is>
-          <t>3502245376</t>
+          <t>3502469834</t>
         </is>
       </c>
       <c r="G58" s="6" t="inlineStr">
         <is>
-          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
-        </is>
-      </c>
-      <c r="H58" s="7"/>
-      <c r="I58" s="6"/>
-      <c r="J58" s="6"/>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H58" s="7" t="inlineStr">
+        <is>
+          <t>0317226849</t>
+        </is>
+      </c>
+      <c r="I58" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH GIẢI PHÁP CPE</t>
+        </is>
+      </c>
+      <c r="J58" s="6" t="inlineStr">
+        <is>
+          <t>Số 490 Đường Phạm Thái Bường,Phường Tân Hưng,Thành phố Hồ Chí Minh,Việt Nam</t>
+        </is>
+      </c>
       <c r="K58" s="6"/>
       <c r="L58" s="13" t="n">
-        <v>83333.0</v>
+        <v>3038656.0</v>
       </c>
       <c r="M58" s="13" t="n">
-        <v>6667.0</v>
+        <v>243092.0</v>
       </c>
       <c r="N58" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O58" s="13" t="n">
-        <v>90000.0</v>
+        <v>3281748.0</v>
       </c>
       <c r="P58" s="6" t="inlineStr">
         <is>
@@ -3469,6 +4041,1308 @@
         </is>
       </c>
       <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>53.0</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>813</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2025</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H59" s="7" t="inlineStr">
+        <is>
+          <t>0303625152</t>
+        </is>
+      </c>
+      <c r="I59" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH DU LỊCH - DỊCH VỤ VÀ THƯƠNG MẠI SEN VIỆT</t>
+        </is>
+      </c>
+      <c r="J59" s="6" t="inlineStr">
+        <is>
+          <t>85 Điện Biên Phủ, Phường Tân Định, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K59" s="6"/>
+      <c r="L59" s="13" t="n">
+        <v>6146586.0</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>491727.0</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>6638313.0</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>54.0</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>814</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>15/10/2025</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H60" s="7" t="inlineStr">
+        <is>
+          <t>3500122361</t>
+        </is>
+      </c>
+      <c r="I60" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH - TẬP ĐOÀN HẢI CHÂU VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="J60" s="6" t="inlineStr">
+        <is>
+          <t>Số 155 Lê Hồng Phong,Phường Tam Thắng,Thành phố Hồ Chí Minh,Việt Nam</t>
+        </is>
+      </c>
+      <c r="K60" s="6"/>
+      <c r="L60" s="13" t="n">
+        <v>3159388.0</v>
+      </c>
+      <c r="M60" s="13" t="n">
+        <v>252751.0</v>
+      </c>
+      <c r="N60" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O60" s="13" t="n">
+        <v>3412139.0</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>55.0</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>815</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>16/10/2025</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H61" s="7" t="inlineStr">
+        <is>
+          <t>0305280954</t>
+        </is>
+      </c>
+      <c r="I61" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN SẢN XUẤT VÀ CÔNG NGHỆ BÁCH VIỆT</t>
+        </is>
+      </c>
+      <c r="J61" s="6" t="inlineStr">
+        <is>
+          <t>11/11 Đường Nguyễn Văn Mại, phường Tân Sơn Nhất, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K61" s="6"/>
+      <c r="L61" s="13" t="n">
+        <v>1006608.0</v>
+      </c>
+      <c r="M61" s="13" t="n">
+        <v>80529.0</v>
+      </c>
+      <c r="N61" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O61" s="13" t="n">
+        <v>1087137.0</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>816</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>16/10/2025</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H62" s="7" t="inlineStr">
+        <is>
+          <t>3500106440</t>
+        </is>
+      </c>
+      <c r="I62" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH INTERNATIONAL SOS VIỆT NAM</t>
+        </is>
+      </c>
+      <c r="J62" s="6" t="inlineStr">
+        <is>
+          <t>106 Nguyễn Văn Trỗi, Phường Phú Nhuận, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K62" s="6"/>
+      <c r="L62" s="13" t="n">
+        <v>2602382.0</v>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>208191.0</v>
+      </c>
+      <c r="N62" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O62" s="13" t="n">
+        <v>2810573.0</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>57.0</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>817</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H63" s="7" t="inlineStr">
+        <is>
+          <t>3500834094</t>
+        </is>
+      </c>
+      <c r="I63" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN KẾT CẤU KIM LOẠI VÀ LẮP MÁY DẦU KHÍ</t>
+        </is>
+      </c>
+      <c r="J63" s="6" t="inlineStr">
+        <is>
+          <t>Số 2 Nguyễn Hữu Cảnh,Phường Rạch Dừa,Thành phố Hồ Chí Minh,Việt Nam</t>
+        </is>
+      </c>
+      <c r="K63" s="6"/>
+      <c r="L63" s="13" t="n">
+        <v>3818516.0</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>305481.0</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>4123997.0</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>818</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H64" s="7" t="inlineStr">
+        <is>
+          <t>0105402531-017</t>
+        </is>
+      </c>
+      <c r="I64" s="6" t="inlineStr">
+        <is>
+          <t>Công ty Bảo Hiểm PVI Vũng Tàu</t>
+        </is>
+      </c>
+      <c r="J64" s="6" t="inlineStr">
+        <is>
+          <t>Số 58A Võ Thị Sáu,Phường Vũng Tàu,Thành phố Hồ Chí Minh,Việt Nam</t>
+        </is>
+      </c>
+      <c r="K64" s="6"/>
+      <c r="L64" s="13" t="n">
+        <v>1417052.0</v>
+      </c>
+      <c r="M64" s="13" t="n">
+        <v>113364.0</v>
+      </c>
+      <c r="N64" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O64" s="13" t="n">
+        <v>1530416.0</v>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>59.0</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>819</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H65" s="7" t="inlineStr">
+        <is>
+          <t>3502392797</t>
+        </is>
+      </c>
+      <c r="I65" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH PHÚ ĐỨC VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J65" s="6" t="inlineStr">
+        <is>
+          <t>209 đường Võ Thị Sáu, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K65" s="6"/>
+      <c r="L65" s="13" t="n">
+        <v>2278510.0</v>
+      </c>
+      <c r="M65" s="13" t="n">
+        <v>182281.0</v>
+      </c>
+      <c r="N65" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O65" s="13" t="n">
+        <v>2460791.0</v>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q65" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>60.0</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>820</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>18/10/2025</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H66" s="7"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="13" t="n">
+        <v>1805295.0</v>
+      </c>
+      <c r="M66" s="13" t="n">
+        <v>144424.0</v>
+      </c>
+      <c r="N66" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O66" s="13" t="n">
+        <v>1949719.0</v>
+      </c>
+      <c r="P66" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q66" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>61.0</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>821</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>19/10/2025</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H67" s="7" t="inlineStr">
+        <is>
+          <t>3502524073</t>
+        </is>
+      </c>
+      <c r="I67" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH QUỐC BẢO VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J67" s="6" t="inlineStr">
+        <is>
+          <t>18 Huỳnh Khương An,Phường Vũng Tàu,Thành phố Hồ Chí Minh,Việt Nam</t>
+        </is>
+      </c>
+      <c r="K67" s="6"/>
+      <c r="L67" s="13" t="n">
+        <v>405000.0</v>
+      </c>
+      <c r="M67" s="13" t="n">
+        <v>40500.0</v>
+      </c>
+      <c r="N67" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O67" s="13" t="n">
+        <v>445500.0</v>
+      </c>
+      <c r="P67" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q67" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="n">
+        <v>62.0</v>
+      </c>
+      <c r="B68" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C68" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D68" s="7" t="inlineStr">
+        <is>
+          <t>822</t>
+        </is>
+      </c>
+      <c r="E68" s="7" t="inlineStr">
+        <is>
+          <t>19/10/2025</t>
+        </is>
+      </c>
+      <c r="F68" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G68" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H68" s="7" t="inlineStr">
+        <is>
+          <t>3502524073</t>
+        </is>
+      </c>
+      <c r="I68" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH QUỐC BẢO VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J68" s="6" t="inlineStr">
+        <is>
+          <t>18 Huỳnh Khương An,Phường Vũng Tàu,Thành phố Hồ Chí Minh,Việt Nam</t>
+        </is>
+      </c>
+      <c r="K68" s="6"/>
+      <c r="L68" s="13" t="n">
+        <v>858156.0</v>
+      </c>
+      <c r="M68" s="13" t="n">
+        <v>68652.0</v>
+      </c>
+      <c r="N68" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O68" s="13" t="n">
+        <v>926808.0</v>
+      </c>
+      <c r="P68" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q68" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="n">
+        <v>63.0</v>
+      </c>
+      <c r="B69" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C69" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D69" s="7" t="inlineStr">
+        <is>
+          <t>823</t>
+        </is>
+      </c>
+      <c r="E69" s="7" t="inlineStr">
+        <is>
+          <t>19/10/2025</t>
+        </is>
+      </c>
+      <c r="F69" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H69" s="7" t="inlineStr">
+        <is>
+          <t>2901270911</t>
+        </is>
+      </c>
+      <c r="I69" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN CHUỖI THỰC PHẨM TH</t>
+        </is>
+      </c>
+      <c r="J69" s="6" t="inlineStr">
+        <is>
+          <t>Số 166, đường Nguyễn Thái Học, Phường Thành Vinh, Tỉnh Nghệ An, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K69" s="6"/>
+      <c r="L69" s="13" t="n">
+        <v>1348738.0</v>
+      </c>
+      <c r="M69" s="13" t="n">
+        <v>107899.0</v>
+      </c>
+      <c r="N69" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O69" s="13" t="n">
+        <v>1456637.0</v>
+      </c>
+      <c r="P69" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q69" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="n">
+        <v>64.0</v>
+      </c>
+      <c r="B70" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D70" s="7" t="inlineStr">
+        <is>
+          <t>824</t>
+        </is>
+      </c>
+      <c r="E70" s="7" t="inlineStr">
+        <is>
+          <t>19/10/2025</t>
+        </is>
+      </c>
+      <c r="F70" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G70" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H70" s="7" t="inlineStr">
+        <is>
+          <t>0100150577-033</t>
+        </is>
+      </c>
+      <c r="I70" s="6" t="inlineStr">
+        <is>
+          <t>CHI NHÁNH TỔNG CÔNG TY CỔ PHẦN DỊCH VỤ KỸ THUẬT DẦU KHÍ VIỆT NAM- CÔNG TY CẢNG DỊCH VỤ DẦU KHÍ</t>
+        </is>
+      </c>
+      <c r="J70" s="6" t="inlineStr">
+        <is>
+          <t>Số 65A đường 30/4, Phường Rạch Dừa, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K70" s="6"/>
+      <c r="L70" s="13" t="n">
+        <v>2991983.0</v>
+      </c>
+      <c r="M70" s="13" t="n">
+        <v>239359.0</v>
+      </c>
+      <c r="N70" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O70" s="13" t="n">
+        <v>3231342.0</v>
+      </c>
+      <c r="P70" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q70" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="n">
+        <v>65.0</v>
+      </c>
+      <c r="B71" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C71" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D71" s="7" t="inlineStr">
+        <is>
+          <t>825</t>
+        </is>
+      </c>
+      <c r="E71" s="7" t="inlineStr">
+        <is>
+          <t>19/10/2025</t>
+        </is>
+      </c>
+      <c r="F71" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G71" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H71" s="7" t="inlineStr">
+        <is>
+          <t>0100112437-200</t>
+        </is>
+      </c>
+      <c r="I71" s="6" t="inlineStr">
+        <is>
+          <t>NGÂN HÀNG TMCP NGOẠI THƯƠNG VIỆT NAM - CHI NHÁNH PHÚ MỸ</t>
+        </is>
+      </c>
+      <c r="J71" s="6" t="inlineStr">
+        <is>
+          <t>2315 đường Độc Lập, Phường Phú Mỹ, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K71" s="6"/>
+      <c r="L71" s="13" t="n">
+        <v>1846241.0</v>
+      </c>
+      <c r="M71" s="13" t="n">
+        <v>147699.0</v>
+      </c>
+      <c r="N71" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O71" s="13" t="n">
+        <v>1993940.0</v>
+      </c>
+      <c r="P71" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q71" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="n">
+        <v>66.0</v>
+      </c>
+      <c r="B72" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D72" s="7" t="inlineStr">
+        <is>
+          <t>826</t>
+        </is>
+      </c>
+      <c r="E72" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F72" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G72" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H72" s="7" t="inlineStr">
+        <is>
+          <t>0100110768-023</t>
+        </is>
+      </c>
+      <c r="I72" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY BẢO HIỂM PJICO VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="J72" s="6" t="inlineStr">
+        <is>
+          <t>70 Cô Giang, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K72" s="6"/>
+      <c r="L72" s="13" t="n">
+        <v>1775704.0</v>
+      </c>
+      <c r="M72" s="13" t="n">
+        <v>142056.0</v>
+      </c>
+      <c r="N72" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O72" s="13" t="n">
+        <v>1917760.0</v>
+      </c>
+      <c r="P72" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q72" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="n">
+        <v>67.0</v>
+      </c>
+      <c r="B73" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D73" s="7" t="inlineStr">
+        <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="E73" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F73" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G73" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H73" s="7" t="inlineStr">
+        <is>
+          <t>3502401480</t>
+        </is>
+      </c>
+      <c r="I73" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ ĐẦU TƯ XUẤT NHẬP KHẨU AN PHÁT</t>
+        </is>
+      </c>
+      <c r="J73" s="6" t="inlineStr">
+        <is>
+          <t>Số 441/36 Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K73" s="6"/>
+      <c r="L73" s="13" t="n">
+        <v>495000.0</v>
+      </c>
+      <c r="M73" s="13" t="n">
+        <v>49500.0</v>
+      </c>
+      <c r="N73" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O73" s="13" t="n">
+        <v>544500.0</v>
+      </c>
+      <c r="P73" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q73" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="n">
+        <v>68.0</v>
+      </c>
+      <c r="B74" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D74" s="7" t="inlineStr">
+        <is>
+          <t>828</t>
+        </is>
+      </c>
+      <c r="E74" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F74" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G74" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H74" s="7" t="inlineStr">
+        <is>
+          <t>3502401480</t>
+        </is>
+      </c>
+      <c r="I74" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH THƯƠNG MẠI DỊCH VỤ ĐẦU TƯ XUẤT NHẬP KHẨU AN PHÁT</t>
+        </is>
+      </c>
+      <c r="J74" s="6" t="inlineStr">
+        <is>
+          <t>Số 441/36 Trần Phú, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K74" s="6"/>
+      <c r="L74" s="13" t="n">
+        <v>664992.0</v>
+      </c>
+      <c r="M74" s="13" t="n">
+        <v>53199.0</v>
+      </c>
+      <c r="N74" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O74" s="13" t="n">
+        <v>718191.0</v>
+      </c>
+      <c r="P74" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q74" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="n">
+        <v>69.0</v>
+      </c>
+      <c r="B75" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D75" s="7" t="inlineStr">
+        <is>
+          <t>829</t>
+        </is>
+      </c>
+      <c r="E75" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F75" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G75" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H75" s="7" t="inlineStr">
+        <is>
+          <t>3502348597</t>
+        </is>
+      </c>
+      <c r="I75" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN QUẢNG CÁO HOÀNG KHIÊM</t>
+        </is>
+      </c>
+      <c r="J75" s="6" t="inlineStr">
+        <is>
+          <t>Số 45 Trần Quang Diệu, Phường  Tam Thắng, Thành Phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K75" s="6"/>
+      <c r="L75" s="13" t="n">
+        <v>4532598.0</v>
+      </c>
+      <c r="M75" s="13" t="n">
+        <v>362608.0</v>
+      </c>
+      <c r="N75" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O75" s="13" t="n">
+        <v>4895206.0</v>
+      </c>
+      <c r="P75" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q75" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="n">
+        <v>70.0</v>
+      </c>
+      <c r="B76" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>C25MVP</t>
+        </is>
+      </c>
+      <c r="D76" s="7" t="inlineStr">
+        <is>
+          <t>830</t>
+        </is>
+      </c>
+      <c r="E76" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F76" s="7" t="inlineStr">
+        <is>
+          <t>3502469834</t>
+        </is>
+      </c>
+      <c r="G76" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH MỘT THÀNH VIÊN VƯỜN PHỐ VŨNG TÀU</t>
+        </is>
+      </c>
+      <c r="H76" s="7" t="inlineStr">
+        <is>
+          <t>3502504260</t>
+        </is>
+      </c>
+      <c r="I76" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY TNHH KỸ THUẬT PTK</t>
+        </is>
+      </c>
+      <c r="J76" s="6" t="inlineStr">
+        <is>
+          <t>36/34 Nguyễn Gia Thiều, Phường Phước Thắng, Thành phố Hồ Chí Minh, Việt Nam</t>
+        </is>
+      </c>
+      <c r="K76" s="6"/>
+      <c r="L76" s="13" t="n">
+        <v>1805080.0</v>
+      </c>
+      <c r="M76" s="13" t="n">
+        <v>144406.0</v>
+      </c>
+      <c r="N76" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O76" s="13" t="n">
+        <v>1949486.0</v>
+      </c>
+      <c r="P76" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q76" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>

--- a/Hoadon/HDRa/10/HDDienTuMayTinhTien.xlsx
+++ b/Hoadon/HDRa/10/HDDienTuMayTinhTien.xlsx
@@ -313,56 +313,44 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>C25MAA</t>
+          <t>C25MYY</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>281</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>3500826826</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Nguyên Khang</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
-        <is>
-          <t>3501677542</t>
-        </is>
-      </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TRÁCH NHIỆM HỮU HẠN NỘI THẤT THIÊN LỘC</t>
-        </is>
-      </c>
-      <c r="J7" s="6" t="inlineStr">
-        <is>
-          <t>Số 217 Võ Thị Sáu, Phường Vũng Tàu, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H7" s="7"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
       <c r="K7" s="6"/>
       <c r="L7" s="13" t="n">
-        <v>9334000.0</v>
+        <v>787626.0</v>
       </c>
       <c r="M7" s="13" t="n">
-        <v>746720.0</v>
+        <v>64374.0</v>
       </c>
       <c r="N7" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O7" s="13" t="n">
-        <v>1.008072E7</v>
+        <v>852000.0</v>
       </c>
       <c r="P7" s="6" t="inlineStr">
         <is>
@@ -386,56 +374,44 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>C25MAA</t>
+          <t>C25MYY</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>282</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>02/10/2025</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>3500826826</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Nguyên Khang</t>
-        </is>
-      </c>
-      <c r="H8" s="7" t="inlineStr">
-        <is>
-          <t>3502530503</t>
-        </is>
-      </c>
-      <c r="I8" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THIẾT BỊ ĐIỆN VÀ Y TẾ HUY HOÀN</t>
-        </is>
-      </c>
-      <c r="J8" s="6" t="inlineStr">
-        <is>
-          <t>Quốc lộ 51, tổ 2, Khu phố Song Vĩnh, Phường Tân Phước, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H8" s="7"/>
+      <c r="I8" s="6"/>
+      <c r="J8" s="6"/>
       <c r="K8" s="6"/>
       <c r="L8" s="13" t="n">
-        <v>4.49355E7</v>
+        <v>578519.0</v>
       </c>
       <c r="M8" s="13" t="n">
-        <v>4493550.0</v>
+        <v>41481.0</v>
       </c>
       <c r="N8" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O8" s="13" t="n">
-        <v>4.942905E7</v>
+        <v>620000.0</v>
       </c>
       <c r="P8" s="6" t="inlineStr">
         <is>
@@ -459,56 +435,44 @@
       </c>
       <c r="C9" s="6" t="inlineStr">
         <is>
-          <t>C25MAA</t>
+          <t>C25MYY</t>
         </is>
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>17</t>
+          <t>283</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>06/10/2025</t>
+          <t>03/10/2025</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>3500826826</t>
+          <t>3502245376</t>
         </is>
       </c>
       <c r="G9" s="6" t="inlineStr">
         <is>
-          <t>Công Ty TNHH Nguyên Khang</t>
-        </is>
-      </c>
-      <c r="H9" s="7" t="inlineStr">
-        <is>
-          <t>3502530503</t>
-        </is>
-      </c>
-      <c r="I9" s="6" t="inlineStr">
-        <is>
-          <t>CÔNG TY TNHH THIẾT BỊ ĐIỆN VÀ Y TẾ HUY HOÀN</t>
-        </is>
-      </c>
-      <c r="J9" s="6" t="inlineStr">
-        <is>
-          <t>Quốc lộ 51, tổ 2, Khu phố Song Vĩnh, Phường Tân Phước, Thành phố Hồ Chí Minh, Việt Nam</t>
-        </is>
-      </c>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H9" s="7"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
       <c r="K9" s="6"/>
       <c r="L9" s="13" t="n">
-        <v>4.8825E7</v>
+        <v>793637.0</v>
       </c>
       <c r="M9" s="13" t="n">
-        <v>3906000.0</v>
+        <v>46363.0</v>
       </c>
       <c r="N9" s="13" t="n">
         <v>0.0</v>
       </c>
       <c r="O9" s="13" t="n">
-        <v>5.2731E7</v>
+        <v>840000.0</v>
       </c>
       <c r="P9" s="6" t="inlineStr">
         <is>
@@ -516,6 +480,3544 @@
         </is>
       </c>
       <c r="Q9" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="n">
+        <v>4.0</v>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>03/10/2025</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G10" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H10" s="7"/>
+      <c r="I10" s="6"/>
+      <c r="J10" s="6"/>
+      <c r="K10" s="6"/>
+      <c r="L10" s="13" t="n">
+        <v>822222.0</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>65778.0</v>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O10" s="13" t="n">
+        <v>888000.0</v>
+      </c>
+      <c r="P10" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q10" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="n">
+        <v>5.0</v>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="inlineStr">
+        <is>
+          <t>285</t>
+        </is>
+      </c>
+      <c r="E11" s="7" t="inlineStr">
+        <is>
+          <t>03/10/2025</t>
+        </is>
+      </c>
+      <c r="F11" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G11" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H11" s="7"/>
+      <c r="I11" s="6"/>
+      <c r="J11" s="6"/>
+      <c r="K11" s="6"/>
+      <c r="L11" s="13" t="n">
+        <v>741818.0</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>74182.0</v>
+      </c>
+      <c r="N11" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O11" s="13" t="n">
+        <v>816000.0</v>
+      </c>
+      <c r="P11" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q11" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="n">
+        <v>6.0</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>286</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>04/10/2025</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H12" s="7"/>
+      <c r="I12" s="6"/>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6"/>
+      <c r="L12" s="13" t="n">
+        <v>744444.0</v>
+      </c>
+      <c r="M12" s="13" t="n">
+        <v>35556.0</v>
+      </c>
+      <c r="N12" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O12" s="13" t="n">
+        <v>780000.0</v>
+      </c>
+      <c r="P12" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q12" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="n">
+        <v>7.0</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>287</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>04/10/2025</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G13" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H13" s="7"/>
+      <c r="I13" s="6"/>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6"/>
+      <c r="L13" s="13" t="n">
+        <v>657407.0</v>
+      </c>
+      <c r="M13" s="13" t="n">
+        <v>52593.0</v>
+      </c>
+      <c r="N13" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O13" s="13" t="n">
+        <v>710000.0</v>
+      </c>
+      <c r="P13" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q13" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="n">
+        <v>8.0</v>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D14" s="7" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>05/10/2025</t>
+        </is>
+      </c>
+      <c r="F14" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G14" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H14" s="7"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6"/>
+      <c r="L14" s="13" t="n">
+        <v>942862.0</v>
+      </c>
+      <c r="M14" s="13" t="n">
+        <v>91138.0</v>
+      </c>
+      <c r="N14" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O14" s="13" t="n">
+        <v>1034000.0</v>
+      </c>
+      <c r="P14" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q14" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="n">
+        <v>9.0</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D15" s="7" t="inlineStr">
+        <is>
+          <t>289</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>05/10/2025</t>
+        </is>
+      </c>
+      <c r="F15" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H15" s="7"/>
+      <c r="I15" s="6"/>
+      <c r="J15" s="6"/>
+      <c r="K15" s="6"/>
+      <c r="L15" s="13" t="n">
+        <v>1110908.0</v>
+      </c>
+      <c r="M15" s="13" t="n">
+        <v>90092.0</v>
+      </c>
+      <c r="N15" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O15" s="13" t="n">
+        <v>1201000.0</v>
+      </c>
+      <c r="P15" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q15" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="n">
+        <v>10.0</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D16" s="7" t="inlineStr">
+        <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>05/10/2025</t>
+        </is>
+      </c>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G16" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H16" s="7"/>
+      <c r="I16" s="6"/>
+      <c r="J16" s="6"/>
+      <c r="K16" s="6"/>
+      <c r="L16" s="13" t="n">
+        <v>1034005.0</v>
+      </c>
+      <c r="M16" s="13" t="n">
+        <v>82995.0</v>
+      </c>
+      <c r="N16" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O16" s="13" t="n">
+        <v>1117000.0</v>
+      </c>
+      <c r="P16" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q16" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="n">
+        <v>11.0</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D17" s="7" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="E17" s="7" t="inlineStr">
+        <is>
+          <t>05/10/2025</t>
+        </is>
+      </c>
+      <c r="F17" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G17" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H17" s="7"/>
+      <c r="I17" s="6"/>
+      <c r="J17" s="6"/>
+      <c r="K17" s="6"/>
+      <c r="L17" s="13" t="n">
+        <v>691482.0</v>
+      </c>
+      <c r="M17" s="13" t="n">
+        <v>38518.0</v>
+      </c>
+      <c r="N17" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O17" s="13" t="n">
+        <v>730000.0</v>
+      </c>
+      <c r="P17" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q17" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="n">
+        <v>12.0</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D18" s="7" t="inlineStr">
+        <is>
+          <t>292</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F18" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H18" s="7"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="6"/>
+      <c r="K18" s="6"/>
+      <c r="L18" s="13" t="n">
+        <v>1169630.0</v>
+      </c>
+      <c r="M18" s="13" t="n">
+        <v>50370.0</v>
+      </c>
+      <c r="N18" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O18" s="13" t="n">
+        <v>1220000.0</v>
+      </c>
+      <c r="P18" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q18" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="n">
+        <v>13.0</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D19" s="7" t="inlineStr">
+        <is>
+          <t>293</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>06/10/2025</t>
+        </is>
+      </c>
+      <c r="F19" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G19" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H19" s="7"/>
+      <c r="I19" s="6"/>
+      <c r="J19" s="6"/>
+      <c r="K19" s="6"/>
+      <c r="L19" s="13" t="n">
+        <v>768519.0</v>
+      </c>
+      <c r="M19" s="13" t="n">
+        <v>61481.0</v>
+      </c>
+      <c r="N19" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O19" s="13" t="n">
+        <v>830000.0</v>
+      </c>
+      <c r="P19" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q19" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="n">
+        <v>14.0</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>294</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H20" s="7"/>
+      <c r="I20" s="6"/>
+      <c r="J20" s="6"/>
+      <c r="K20" s="6"/>
+      <c r="L20" s="13" t="n">
+        <v>564815.0</v>
+      </c>
+      <c r="M20" s="13" t="n">
+        <v>45185.0</v>
+      </c>
+      <c r="N20" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O20" s="13" t="n">
+        <v>610000.0</v>
+      </c>
+      <c r="P20" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q20" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="4" t="n">
+        <v>15.0</v>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D21" s="7" t="inlineStr">
+        <is>
+          <t>295</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>07/10/2025</t>
+        </is>
+      </c>
+      <c r="F21" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H21" s="7"/>
+      <c r="I21" s="6"/>
+      <c r="J21" s="6"/>
+      <c r="K21" s="6"/>
+      <c r="L21" s="13" t="n">
+        <v>935186.0</v>
+      </c>
+      <c r="M21" s="13" t="n">
+        <v>74814.0</v>
+      </c>
+      <c r="N21" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O21" s="13" t="n">
+        <v>1010000.0</v>
+      </c>
+      <c r="P21" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q21" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="4" t="n">
+        <v>16.0</v>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>08/10/2025</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G22" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H22" s="7"/>
+      <c r="I22" s="6"/>
+      <c r="J22" s="6"/>
+      <c r="K22" s="6"/>
+      <c r="L22" s="13" t="n">
+        <v>814815.0</v>
+      </c>
+      <c r="M22" s="13" t="n">
+        <v>65185.0</v>
+      </c>
+      <c r="N22" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O22" s="13" t="n">
+        <v>880000.0</v>
+      </c>
+      <c r="P22" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q22" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="n">
+        <v>17.0</v>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D23" s="7" t="inlineStr">
+        <is>
+          <t>297</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>08/10/2025</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G23" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H23" s="7"/>
+      <c r="I23" s="6"/>
+      <c r="J23" s="6"/>
+      <c r="K23" s="6"/>
+      <c r="L23" s="13" t="n">
+        <v>787037.0</v>
+      </c>
+      <c r="M23" s="13" t="n">
+        <v>62963.0</v>
+      </c>
+      <c r="N23" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O23" s="13" t="n">
+        <v>850000.0</v>
+      </c>
+      <c r="P23" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q23" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="n">
+        <v>18.0</v>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D24" s="7" t="inlineStr">
+        <is>
+          <t>298</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>09/10/2025</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G24" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H24" s="7"/>
+      <c r="I24" s="6"/>
+      <c r="J24" s="6"/>
+      <c r="K24" s="6"/>
+      <c r="L24" s="13" t="n">
+        <v>967594.0</v>
+      </c>
+      <c r="M24" s="13" t="n">
+        <v>77406.0</v>
+      </c>
+      <c r="N24" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O24" s="13" t="n">
+        <v>1045000.0</v>
+      </c>
+      <c r="P24" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q24" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="n">
+        <v>19.0</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D25" s="7" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="E25" s="7" t="inlineStr">
+        <is>
+          <t>09/10/2025</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G25" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H25" s="7"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="13" t="n">
+        <v>740740.0</v>
+      </c>
+      <c r="M25" s="13" t="n">
+        <v>59260.0</v>
+      </c>
+      <c r="N25" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O25" s="13" t="n">
+        <v>800000.0</v>
+      </c>
+      <c r="P25" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q25" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="4" t="n">
+        <v>20.0</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D26" s="7" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="E26" s="7" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G26" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H26" s="7"/>
+      <c r="I26" s="6"/>
+      <c r="J26" s="6"/>
+      <c r="K26" s="6"/>
+      <c r="L26" s="13" t="n">
+        <v>744782.0</v>
+      </c>
+      <c r="M26" s="13" t="n">
+        <v>60218.0</v>
+      </c>
+      <c r="N26" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O26" s="13" t="n">
+        <v>805000.0</v>
+      </c>
+      <c r="P26" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q26" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="n">
+        <v>21.0</v>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D27" s="7" t="inlineStr">
+        <is>
+          <t>301</t>
+        </is>
+      </c>
+      <c r="E27" s="7" t="inlineStr">
+        <is>
+          <t>10/10/2025</t>
+        </is>
+      </c>
+      <c r="F27" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G27" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H27" s="7"/>
+      <c r="I27" s="6"/>
+      <c r="J27" s="6"/>
+      <c r="K27" s="6"/>
+      <c r="L27" s="13" t="n">
+        <v>907407.0</v>
+      </c>
+      <c r="M27" s="13" t="n">
+        <v>72593.0</v>
+      </c>
+      <c r="N27" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O27" s="13" t="n">
+        <v>980000.0</v>
+      </c>
+      <c r="P27" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q27" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="n">
+        <v>22.0</v>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D28" s="7" t="inlineStr">
+        <is>
+          <t>302</t>
+        </is>
+      </c>
+      <c r="E28" s="7" t="inlineStr">
+        <is>
+          <t>11/10/2025</t>
+        </is>
+      </c>
+      <c r="F28" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H28" s="7"/>
+      <c r="I28" s="6"/>
+      <c r="J28" s="6"/>
+      <c r="K28" s="6"/>
+      <c r="L28" s="13" t="n">
+        <v>1037038.0</v>
+      </c>
+      <c r="M28" s="13" t="n">
+        <v>82962.0</v>
+      </c>
+      <c r="N28" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O28" s="13" t="n">
+        <v>1120000.0</v>
+      </c>
+      <c r="P28" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q28" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="n">
+        <v>23.0</v>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D29" s="7" t="inlineStr">
+        <is>
+          <t>303</t>
+        </is>
+      </c>
+      <c r="E29" s="7" t="inlineStr">
+        <is>
+          <t>11/10/2025</t>
+        </is>
+      </c>
+      <c r="F29" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G29" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H29" s="7"/>
+      <c r="I29" s="6"/>
+      <c r="J29" s="6"/>
+      <c r="K29" s="6"/>
+      <c r="L29" s="13" t="n">
+        <v>1101851.0</v>
+      </c>
+      <c r="M29" s="13" t="n">
+        <v>88149.0</v>
+      </c>
+      <c r="N29" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O29" s="13" t="n">
+        <v>1190000.0</v>
+      </c>
+      <c r="P29" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q29" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="4" t="n">
+        <v>24.0</v>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>304</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>12/10/2025</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G30" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H30" s="7"/>
+      <c r="I30" s="6"/>
+      <c r="J30" s="6"/>
+      <c r="K30" s="6"/>
+      <c r="L30" s="13" t="n">
+        <v>879629.0</v>
+      </c>
+      <c r="M30" s="13" t="n">
+        <v>70371.0</v>
+      </c>
+      <c r="N30" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O30" s="13" t="n">
+        <v>950000.0</v>
+      </c>
+      <c r="P30" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q30" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="4" t="n">
+        <v>25.0</v>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D31" s="7" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="E31" s="7" t="inlineStr">
+        <is>
+          <t>12/10/2025</t>
+        </is>
+      </c>
+      <c r="F31" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G31" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H31" s="7"/>
+      <c r="I31" s="6"/>
+      <c r="J31" s="6"/>
+      <c r="K31" s="6"/>
+      <c r="L31" s="13" t="n">
+        <v>916666.0</v>
+      </c>
+      <c r="M31" s="13" t="n">
+        <v>73334.0</v>
+      </c>
+      <c r="N31" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O31" s="13" t="n">
+        <v>990000.0</v>
+      </c>
+      <c r="P31" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q31" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="n">
+        <v>26.0</v>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C32" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D32" s="7" t="inlineStr">
+        <is>
+          <t>306</t>
+        </is>
+      </c>
+      <c r="E32" s="7" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F32" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H32" s="7"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="6"/>
+      <c r="K32" s="6"/>
+      <c r="L32" s="13" t="n">
+        <v>682407.0</v>
+      </c>
+      <c r="M32" s="13" t="n">
+        <v>54593.0</v>
+      </c>
+      <c r="N32" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O32" s="13" t="n">
+        <v>737000.0</v>
+      </c>
+      <c r="P32" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q32" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="4" t="n">
+        <v>27.0</v>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C33" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="inlineStr">
+        <is>
+          <t>307</t>
+        </is>
+      </c>
+      <c r="E33" s="7" t="inlineStr">
+        <is>
+          <t>13/10/2025</t>
+        </is>
+      </c>
+      <c r="F33" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G33" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H33" s="7"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="6"/>
+      <c r="K33" s="6"/>
+      <c r="L33" s="13" t="n">
+        <v>1037038.0</v>
+      </c>
+      <c r="M33" s="13" t="n">
+        <v>82962.0</v>
+      </c>
+      <c r="N33" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O33" s="13" t="n">
+        <v>1120000.0</v>
+      </c>
+      <c r="P33" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q33" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="n">
+        <v>28.0</v>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="E34" s="7" t="inlineStr">
+        <is>
+          <t>14/10/2025</t>
+        </is>
+      </c>
+      <c r="F34" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G34" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H34" s="7"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="6"/>
+      <c r="K34" s="6"/>
+      <c r="L34" s="13" t="n">
+        <v>925926.0</v>
+      </c>
+      <c r="M34" s="13" t="n">
+        <v>74074.0</v>
+      </c>
+      <c r="N34" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O34" s="13" t="n">
+        <v>1000000.0</v>
+      </c>
+      <c r="P34" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q34" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="n">
+        <v>29.0</v>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D35" s="7" t="inlineStr">
+        <is>
+          <t>309</t>
+        </is>
+      </c>
+      <c r="E35" s="7" t="inlineStr">
+        <is>
+          <t>14/10/2025</t>
+        </is>
+      </c>
+      <c r="F35" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H35" s="7"/>
+      <c r="I35" s="6"/>
+      <c r="J35" s="6"/>
+      <c r="K35" s="6"/>
+      <c r="L35" s="13" t="n">
+        <v>462963.0</v>
+      </c>
+      <c r="M35" s="13" t="n">
+        <v>37037.0</v>
+      </c>
+      <c r="N35" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O35" s="13" t="n">
+        <v>500000.0</v>
+      </c>
+      <c r="P35" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q35" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="4" t="n">
+        <v>30.0</v>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D36" s="7" t="inlineStr">
+        <is>
+          <t>310</t>
+        </is>
+      </c>
+      <c r="E36" s="7" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="F36" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G36" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H36" s="7"/>
+      <c r="I36" s="6"/>
+      <c r="J36" s="6"/>
+      <c r="K36" s="6"/>
+      <c r="L36" s="13" t="n">
+        <v>163637.0</v>
+      </c>
+      <c r="M36" s="13" t="n">
+        <v>16363.0</v>
+      </c>
+      <c r="N36" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O36" s="13" t="n">
+        <v>180000.0</v>
+      </c>
+      <c r="P36" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q36" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="4" t="n">
+        <v>31.0</v>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D37" s="7" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="E37" s="7" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="F37" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G37" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H37" s="7"/>
+      <c r="I37" s="6"/>
+      <c r="J37" s="6"/>
+      <c r="K37" s="6"/>
+      <c r="L37" s="13" t="n">
+        <v>657407.0</v>
+      </c>
+      <c r="M37" s="13" t="n">
+        <v>52593.0</v>
+      </c>
+      <c r="N37" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O37" s="13" t="n">
+        <v>710000.0</v>
+      </c>
+      <c r="P37" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q37" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="4" t="n">
+        <v>32.0</v>
+      </c>
+      <c r="B38" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D38" s="7" t="inlineStr">
+        <is>
+          <t>312</t>
+        </is>
+      </c>
+      <c r="E38" s="7" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="F38" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H38" s="7"/>
+      <c r="I38" s="6"/>
+      <c r="J38" s="6"/>
+      <c r="K38" s="6"/>
+      <c r="L38" s="13" t="n">
+        <v>129629.0</v>
+      </c>
+      <c r="M38" s="13" t="n">
+        <v>10371.0</v>
+      </c>
+      <c r="N38" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O38" s="13" t="n">
+        <v>140000.0</v>
+      </c>
+      <c r="P38" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q38" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="4" t="n">
+        <v>33.0</v>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D39" s="7" t="inlineStr">
+        <is>
+          <t>313</t>
+        </is>
+      </c>
+      <c r="E39" s="7" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="F39" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G39" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H39" s="7"/>
+      <c r="I39" s="6"/>
+      <c r="J39" s="6"/>
+      <c r="K39" s="6"/>
+      <c r="L39" s="13" t="n">
+        <v>83333.0</v>
+      </c>
+      <c r="M39" s="13" t="n">
+        <v>6667.0</v>
+      </c>
+      <c r="N39" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O39" s="13" t="n">
+        <v>90000.0</v>
+      </c>
+      <c r="P39" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q39" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="4" t="n">
+        <v>34.0</v>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G40" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H40" s="7"/>
+      <c r="I40" s="6"/>
+      <c r="J40" s="6"/>
+      <c r="K40" s="6"/>
+      <c r="L40" s="13" t="n">
+        <v>1027777.0</v>
+      </c>
+      <c r="M40" s="13" t="n">
+        <v>82223.0</v>
+      </c>
+      <c r="N40" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O40" s="13" t="n">
+        <v>1110000.0</v>
+      </c>
+      <c r="P40" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q40" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="n">
+        <v>35.0</v>
+      </c>
+      <c r="B41" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C41" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D41" s="7" t="inlineStr">
+        <is>
+          <t>315</t>
+        </is>
+      </c>
+      <c r="E41" s="7" t="inlineStr">
+        <is>
+          <t>17/10/2025</t>
+        </is>
+      </c>
+      <c r="F41" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H41" s="7"/>
+      <c r="I41" s="6"/>
+      <c r="J41" s="6"/>
+      <c r="K41" s="6"/>
+      <c r="L41" s="13" t="n">
+        <v>369361.0</v>
+      </c>
+      <c r="M41" s="13" t="n">
+        <v>30639.0</v>
+      </c>
+      <c r="N41" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O41" s="13" t="n">
+        <v>400000.0</v>
+      </c>
+      <c r="P41" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q41" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="n">
+        <v>36.0</v>
+      </c>
+      <c r="B42" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D42" s="7" t="inlineStr">
+        <is>
+          <t>316</t>
+        </is>
+      </c>
+      <c r="E42" s="7" t="inlineStr">
+        <is>
+          <t>18/10/2025</t>
+        </is>
+      </c>
+      <c r="F42" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G42" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H42" s="7"/>
+      <c r="I42" s="6"/>
+      <c r="J42" s="6"/>
+      <c r="K42" s="6"/>
+      <c r="L42" s="13" t="n">
+        <v>833333.0</v>
+      </c>
+      <c r="M42" s="13" t="n">
+        <v>66667.0</v>
+      </c>
+      <c r="N42" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O42" s="13" t="n">
+        <v>900000.0</v>
+      </c>
+      <c r="P42" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q42" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="n">
+        <v>37.0</v>
+      </c>
+      <c r="B43" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D43" s="7" t="inlineStr">
+        <is>
+          <t>317</t>
+        </is>
+      </c>
+      <c r="E43" s="7" t="inlineStr">
+        <is>
+          <t>18/10/2025</t>
+        </is>
+      </c>
+      <c r="F43" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G43" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H43" s="7"/>
+      <c r="I43" s="6"/>
+      <c r="J43" s="6"/>
+      <c r="K43" s="6"/>
+      <c r="L43" s="13" t="n">
+        <v>166666.0</v>
+      </c>
+      <c r="M43" s="13" t="n">
+        <v>13334.0</v>
+      </c>
+      <c r="N43" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O43" s="13" t="n">
+        <v>180000.0</v>
+      </c>
+      <c r="P43" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q43" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="n">
+        <v>38.0</v>
+      </c>
+      <c r="B44" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D44" s="7" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="E44" s="7" t="inlineStr">
+        <is>
+          <t>18/10/2025</t>
+        </is>
+      </c>
+      <c r="F44" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G44" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H44" s="7"/>
+      <c r="I44" s="6"/>
+      <c r="J44" s="6"/>
+      <c r="K44" s="6"/>
+      <c r="L44" s="13" t="n">
+        <v>694446.0</v>
+      </c>
+      <c r="M44" s="13" t="n">
+        <v>55554.0</v>
+      </c>
+      <c r="N44" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O44" s="13" t="n">
+        <v>750000.0</v>
+      </c>
+      <c r="P44" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q44" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="n">
+        <v>39.0</v>
+      </c>
+      <c r="B45" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D45" s="7" t="inlineStr">
+        <is>
+          <t>319</t>
+        </is>
+      </c>
+      <c r="E45" s="7" t="inlineStr">
+        <is>
+          <t>18/10/2025</t>
+        </is>
+      </c>
+      <c r="F45" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G45" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H45" s="7"/>
+      <c r="I45" s="6"/>
+      <c r="J45" s="6"/>
+      <c r="K45" s="6"/>
+      <c r="L45" s="13" t="n">
+        <v>90909.0</v>
+      </c>
+      <c r="M45" s="13" t="n">
+        <v>9091.0</v>
+      </c>
+      <c r="N45" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O45" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P45" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q45" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="4" t="n">
+        <v>40.0</v>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C46" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>320</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>18/10/2025</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G46" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H46" s="7"/>
+      <c r="I46" s="6"/>
+      <c r="J46" s="6"/>
+      <c r="K46" s="6"/>
+      <c r="L46" s="13" t="n">
+        <v>490741.0</v>
+      </c>
+      <c r="M46" s="13" t="n">
+        <v>39259.0</v>
+      </c>
+      <c r="N46" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O46" s="13" t="n">
+        <v>530000.0</v>
+      </c>
+      <c r="P46" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q46" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="n">
+        <v>41.0</v>
+      </c>
+      <c r="B47" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D47" s="7" t="inlineStr">
+        <is>
+          <t>321</t>
+        </is>
+      </c>
+      <c r="E47" s="7" t="inlineStr">
+        <is>
+          <t>19/10/2025</t>
+        </is>
+      </c>
+      <c r="F47" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G47" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H47" s="7"/>
+      <c r="I47" s="6"/>
+      <c r="J47" s="6"/>
+      <c r="K47" s="6"/>
+      <c r="L47" s="13" t="n">
+        <v>319023.0</v>
+      </c>
+      <c r="M47" s="13" t="n">
+        <v>25977.0</v>
+      </c>
+      <c r="N47" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O47" s="13" t="n">
+        <v>345000.0</v>
+      </c>
+      <c r="P47" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q47" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="4" t="n">
+        <v>42.0</v>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C48" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>322</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>19/10/2025</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G48" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H48" s="7"/>
+      <c r="I48" s="6"/>
+      <c r="J48" s="6"/>
+      <c r="K48" s="6"/>
+      <c r="L48" s="13" t="n">
+        <v>892593.0</v>
+      </c>
+      <c r="M48" s="13" t="n">
+        <v>71407.0</v>
+      </c>
+      <c r="N48" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O48" s="13" t="n">
+        <v>964000.0</v>
+      </c>
+      <c r="P48" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q48" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="n">
+        <v>43.0</v>
+      </c>
+      <c r="B49" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D49" s="7" t="inlineStr">
+        <is>
+          <t>323</t>
+        </is>
+      </c>
+      <c r="E49" s="7" t="inlineStr">
+        <is>
+          <t>19/10/2025</t>
+        </is>
+      </c>
+      <c r="F49" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H49" s="7"/>
+      <c r="I49" s="6"/>
+      <c r="J49" s="6"/>
+      <c r="K49" s="6"/>
+      <c r="L49" s="13" t="n">
+        <v>1055555.0</v>
+      </c>
+      <c r="M49" s="13" t="n">
+        <v>84445.0</v>
+      </c>
+      <c r="N49" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O49" s="13" t="n">
+        <v>1140000.0</v>
+      </c>
+      <c r="P49" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q49" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="n">
+        <v>44.0</v>
+      </c>
+      <c r="B50" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D50" s="7" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="E50" s="7" t="inlineStr">
+        <is>
+          <t>19/10/2025</t>
+        </is>
+      </c>
+      <c r="F50" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G50" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H50" s="7"/>
+      <c r="I50" s="6"/>
+      <c r="J50" s="6"/>
+      <c r="K50" s="6"/>
+      <c r="L50" s="13" t="n">
+        <v>294108.0</v>
+      </c>
+      <c r="M50" s="13" t="n">
+        <v>23892.0</v>
+      </c>
+      <c r="N50" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O50" s="13" t="n">
+        <v>318000.0</v>
+      </c>
+      <c r="P50" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q50" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="n">
+        <v>45.0</v>
+      </c>
+      <c r="B51" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C51" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D51" s="7" t="inlineStr">
+        <is>
+          <t>325</t>
+        </is>
+      </c>
+      <c r="E51" s="7" t="inlineStr">
+        <is>
+          <t>19/10/2025</t>
+        </is>
+      </c>
+      <c r="F51" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H51" s="7"/>
+      <c r="I51" s="6"/>
+      <c r="J51" s="6"/>
+      <c r="K51" s="6"/>
+      <c r="L51" s="13" t="n">
+        <v>92593.0</v>
+      </c>
+      <c r="M51" s="13" t="n">
+        <v>7407.0</v>
+      </c>
+      <c r="N51" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O51" s="13" t="n">
+        <v>100000.0</v>
+      </c>
+      <c r="P51" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q51" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="n">
+        <v>46.0</v>
+      </c>
+      <c r="B52" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D52" s="7" t="inlineStr">
+        <is>
+          <t>326</t>
+        </is>
+      </c>
+      <c r="E52" s="7" t="inlineStr">
+        <is>
+          <t>19/10/2025</t>
+        </is>
+      </c>
+      <c r="F52" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G52" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H52" s="7"/>
+      <c r="I52" s="6"/>
+      <c r="J52" s="6"/>
+      <c r="K52" s="6"/>
+      <c r="L52" s="13" t="n">
+        <v>222222.0</v>
+      </c>
+      <c r="M52" s="13" t="n">
+        <v>17778.0</v>
+      </c>
+      <c r="N52" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O52" s="13" t="n">
+        <v>240000.0</v>
+      </c>
+      <c r="P52" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q52" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="n">
+        <v>47.0</v>
+      </c>
+      <c r="B53" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D53" s="7" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="E53" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F53" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H53" s="7"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
+      <c r="K53" s="6"/>
+      <c r="L53" s="13" t="n">
+        <v>636110.0</v>
+      </c>
+      <c r="M53" s="13" t="n">
+        <v>50890.0</v>
+      </c>
+      <c r="N53" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O53" s="13" t="n">
+        <v>687000.0</v>
+      </c>
+      <c r="P53" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q53" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="n">
+        <v>48.0</v>
+      </c>
+      <c r="B54" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C54" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D54" s="7" t="inlineStr">
+        <is>
+          <t>328</t>
+        </is>
+      </c>
+      <c r="E54" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G54" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H54" s="7"/>
+      <c r="I54" s="6"/>
+      <c r="J54" s="6"/>
+      <c r="K54" s="6"/>
+      <c r="L54" s="13" t="n">
+        <v>333333.0</v>
+      </c>
+      <c r="M54" s="13" t="n">
+        <v>26667.0</v>
+      </c>
+      <c r="N54" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O54" s="13" t="n">
+        <v>360000.0</v>
+      </c>
+      <c r="P54" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q54" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="4" t="n">
+        <v>49.0</v>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H55" s="7"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="6"/>
+      <c r="L55" s="13" t="n">
+        <v>240741.0</v>
+      </c>
+      <c r="M55" s="13" t="n">
+        <v>19259.0</v>
+      </c>
+      <c r="N55" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O55" s="13" t="n">
+        <v>260000.0</v>
+      </c>
+      <c r="P55" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q55" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="n">
+        <v>50.0</v>
+      </c>
+      <c r="B56" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C56" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D56" s="7" t="inlineStr">
+        <is>
+          <t>330</t>
+        </is>
+      </c>
+      <c r="E56" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H56" s="7"/>
+      <c r="I56" s="6"/>
+      <c r="J56" s="6"/>
+      <c r="K56" s="6"/>
+      <c r="L56" s="13" t="n">
+        <v>388889.0</v>
+      </c>
+      <c r="M56" s="13" t="n">
+        <v>31111.0</v>
+      </c>
+      <c r="N56" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O56" s="13" t="n">
+        <v>420000.0</v>
+      </c>
+      <c r="P56" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q56" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="4" t="n">
+        <v>51.0</v>
+      </c>
+      <c r="B57" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C57" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D57" s="7" t="inlineStr">
+        <is>
+          <t>331</t>
+        </is>
+      </c>
+      <c r="E57" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H57" s="7"/>
+      <c r="I57" s="6"/>
+      <c r="J57" s="6"/>
+      <c r="K57" s="6"/>
+      <c r="L57" s="13" t="n">
+        <v>513889.0</v>
+      </c>
+      <c r="M57" s="13" t="n">
+        <v>41111.0</v>
+      </c>
+      <c r="N57" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O57" s="13" t="n">
+        <v>555000.0</v>
+      </c>
+      <c r="P57" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q57" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="4" t="n">
+        <v>52.0</v>
+      </c>
+      <c r="B58" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C58" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D58" s="7" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="E58" s="7" t="inlineStr">
+        <is>
+          <t>20/10/2025</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H58" s="7"/>
+      <c r="I58" s="6"/>
+      <c r="J58" s="6"/>
+      <c r="K58" s="6"/>
+      <c r="L58" s="13" t="n">
+        <v>83333.0</v>
+      </c>
+      <c r="M58" s="13" t="n">
+        <v>6667.0</v>
+      </c>
+      <c r="N58" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O58" s="13" t="n">
+        <v>90000.0</v>
+      </c>
+      <c r="P58" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q58" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="n">
+        <v>53.0</v>
+      </c>
+      <c r="B59" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C59" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D59" s="7" t="inlineStr">
+        <is>
+          <t>333</t>
+        </is>
+      </c>
+      <c r="E59" s="7" t="inlineStr">
+        <is>
+          <t>25/10/2025</t>
+        </is>
+      </c>
+      <c r="F59" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H59" s="7"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="6"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="13" t="n">
+        <v>588722.0</v>
+      </c>
+      <c r="M59" s="13" t="n">
+        <v>47278.0</v>
+      </c>
+      <c r="N59" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O59" s="13" t="n">
+        <v>636000.0</v>
+      </c>
+      <c r="P59" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q59" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="4" t="n">
+        <v>54.0</v>
+      </c>
+      <c r="B60" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C60" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D60" s="7" t="inlineStr">
+        <is>
+          <t>334</t>
+        </is>
+      </c>
+      <c r="E60" s="7" t="inlineStr">
+        <is>
+          <t>25/10/2025</t>
+        </is>
+      </c>
+      <c r="F60" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H60" s="7"/>
+      <c r="I60" s="6"/>
+      <c r="J60" s="6"/>
+      <c r="K60" s="6"/>
+      <c r="L60" s="13" t="n">
+        <v>110775.0</v>
+      </c>
+      <c r="M60" s="13" t="n">
+        <v>9225.0</v>
+      </c>
+      <c r="N60" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O60" s="13" t="n">
+        <v>120000.0</v>
+      </c>
+      <c r="P60" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q60" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="4" t="n">
+        <v>55.0</v>
+      </c>
+      <c r="B61" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C61" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D61" s="7" t="inlineStr">
+        <is>
+          <t>335</t>
+        </is>
+      </c>
+      <c r="E61" s="7" t="inlineStr">
+        <is>
+          <t>25/10/2025</t>
+        </is>
+      </c>
+      <c r="F61" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H61" s="7"/>
+      <c r="I61" s="6"/>
+      <c r="J61" s="6"/>
+      <c r="K61" s="6"/>
+      <c r="L61" s="13" t="n">
+        <v>805555.0</v>
+      </c>
+      <c r="M61" s="13" t="n">
+        <v>64445.0</v>
+      </c>
+      <c r="N61" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O61" s="13" t="n">
+        <v>870000.0</v>
+      </c>
+      <c r="P61" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q61" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="4" t="n">
+        <v>56.0</v>
+      </c>
+      <c r="B62" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C62" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D62" s="7" t="inlineStr">
+        <is>
+          <t>336</t>
+        </is>
+      </c>
+      <c r="E62" s="7" t="inlineStr">
+        <is>
+          <t>25/10/2025</t>
+        </is>
+      </c>
+      <c r="F62" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H62" s="7"/>
+      <c r="I62" s="6"/>
+      <c r="J62" s="6"/>
+      <c r="K62" s="6"/>
+      <c r="L62" s="13" t="n">
+        <v>416667.0</v>
+      </c>
+      <c r="M62" s="13" t="n">
+        <v>33333.0</v>
+      </c>
+      <c r="N62" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O62" s="13" t="n">
+        <v>450000.0</v>
+      </c>
+      <c r="P62" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q62" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="n">
+        <v>57.0</v>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C63" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D63" s="7" t="inlineStr">
+        <is>
+          <t>337</t>
+        </is>
+      </c>
+      <c r="E63" s="7" t="inlineStr">
+        <is>
+          <t>26/10/2025</t>
+        </is>
+      </c>
+      <c r="F63" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H63" s="7"/>
+      <c r="I63" s="6"/>
+      <c r="J63" s="6"/>
+      <c r="K63" s="6"/>
+      <c r="L63" s="13" t="n">
+        <v>634259.0</v>
+      </c>
+      <c r="M63" s="13" t="n">
+        <v>50741.0</v>
+      </c>
+      <c r="N63" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O63" s="13" t="n">
+        <v>685000.0</v>
+      </c>
+      <c r="P63" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q63" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="4" t="n">
+        <v>58.0</v>
+      </c>
+      <c r="B64" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D64" s="7" t="inlineStr">
+        <is>
+          <t>338</t>
+        </is>
+      </c>
+      <c r="E64" s="7" t="inlineStr">
+        <is>
+          <t>26/10/2025</t>
+        </is>
+      </c>
+      <c r="F64" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H64" s="7"/>
+      <c r="I64" s="6"/>
+      <c r="J64" s="6"/>
+      <c r="K64" s="6"/>
+      <c r="L64" s="13" t="n">
+        <v>916667.0</v>
+      </c>
+      <c r="M64" s="13" t="n">
+        <v>73333.0</v>
+      </c>
+      <c r="N64" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O64" s="13" t="n">
+        <v>990000.0</v>
+      </c>
+      <c r="P64" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q64" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="4" t="n">
+        <v>59.0</v>
+      </c>
+      <c r="B65" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C65" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D65" s="7" t="inlineStr">
+        <is>
+          <t>339</t>
+        </is>
+      </c>
+      <c r="E65" s="7" t="inlineStr">
+        <is>
+          <t>26/10/2025</t>
+        </is>
+      </c>
+      <c r="F65" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H65" s="7"/>
+      <c r="I65" s="6"/>
+      <c r="J65" s="6"/>
+      <c r="K65" s="6"/>
+      <c r="L65" s="13" t="n">
+        <v>267676.0</v>
+      </c>
+      <c r="M65" s="13" t="n">
+        <v>22324.0</v>
+      </c>
+      <c r="N65" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O65" s="13" t="n">
+        <v>290000.0</v>
+      </c>
+      <c r="P65" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q65" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="n">
+        <v>60.0</v>
+      </c>
+      <c r="B66" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C66" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D66" s="7" t="inlineStr">
+        <is>
+          <t>340</t>
+        </is>
+      </c>
+      <c r="E66" s="7" t="inlineStr">
+        <is>
+          <t>26/10/2025</t>
+        </is>
+      </c>
+      <c r="F66" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H66" s="7"/>
+      <c r="I66" s="6"/>
+      <c r="J66" s="6"/>
+      <c r="K66" s="6"/>
+      <c r="L66" s="13" t="n">
+        <v>522222.0</v>
+      </c>
+      <c r="M66" s="13" t="n">
+        <v>41778.0</v>
+      </c>
+      <c r="N66" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O66" s="13" t="n">
+        <v>564000.0</v>
+      </c>
+      <c r="P66" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q66" s="6" t="inlineStr">
+        <is>
+          <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="n">
+        <v>61.0</v>
+      </c>
+      <c r="B67" s="7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C67" s="6" t="inlineStr">
+        <is>
+          <t>C25MYY</t>
+        </is>
+      </c>
+      <c r="D67" s="7" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="E67" s="7" t="inlineStr">
+        <is>
+          <t>26/10/2025</t>
+        </is>
+      </c>
+      <c r="F67" s="7" t="inlineStr">
+        <is>
+          <t>3502245376</t>
+        </is>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>CÔNG TY CỔ PHẦN ĐẦU TƯ XÂY DỰNG THƯƠNG MẠI DỊCH VỤ KỸ THUẬT H &amp; V</t>
+        </is>
+      </c>
+      <c r="H67" s="7"/>
+      <c r="I67" s="6"/>
+      <c r="J67" s="6"/>
+      <c r="K67" s="6"/>
+      <c r="L67" s="13" t="n">
+        <v>588889.0</v>
+      </c>
+      <c r="M67" s="13" t="n">
+        <v>47111.0</v>
+      </c>
+      <c r="N67" s="13" t="n">
+        <v>0.0</v>
+      </c>
+      <c r="O67" s="13" t="n">
+        <v>636000.0</v>
+      </c>
+      <c r="P67" s="6" t="inlineStr">
+        <is>
+          <t>Hóa đơn mới</t>
+        </is>
+      </c>
+      <c r="Q67" s="6" t="inlineStr">
         <is>
           <t>Cục Thuế đã nhận hóa đơn có mã khởi tạo từ máy tính tiền</t>
         </is>
